--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\storage.slu.se\home_2$\eoar0001\Documents\ARMELLONI_SLU\RiskAnalysis\LEK\interviews_round2_aug2025\coding\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4CB34B-8BA5-4A0E-83F1-6D5E79956DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D8C614-C522-4B20-BF5F-04C2889480D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38490" yWindow="-11510" windowWidth="19380" windowHeight="20970" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I_1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="178">
   <si>
     <t>If the [extreme event] happen, how likely are you to go out fishing?</t>
   </si>
@@ -534,9 +534,6 @@
     </r>
   </si>
   <si>
-    <t>general</t>
-  </si>
-  <si>
     <t>gear</t>
   </si>
   <si>
@@ -582,7 +579,16 @@
     <t>rod</t>
   </si>
   <si>
-    <t>icefishing</t>
+    <t>ice fishing</t>
+  </si>
+  <si>
+    <t>not_reported</t>
+  </si>
+  <si>
+    <t>additions</t>
+  </si>
+  <si>
+    <t>addit</t>
   </si>
 </sst>
 </file>
@@ -734,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -880,18 +886,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1173,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
@@ -1200,13 +1194,13 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -1268,33 +1262,30 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
-        <v>2</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="23">
-        <v>2</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="43">
-        <v>1</v>
-      </c>
-      <c r="I3" s="23">
-        <v>-999</v>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="27">
+        <v>2</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="45">
+        <v>4</v>
       </c>
       <c r="J3" s="47">
         <v>1</v>
       </c>
-      <c r="K3" s="23">
-        <v>-999</v>
-      </c>
-      <c r="L3" s="23">
-        <v>-999</v>
+      <c r="K3" s="45">
+        <v>1</v>
+      </c>
+      <c r="L3" s="45">
+        <v>1</v>
       </c>
       <c r="M3" s="44">
         <v>5</v>
@@ -1302,84 +1293,51 @@
       <c r="N3" s="43">
         <v>1</v>
       </c>
-      <c r="R3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>2</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="23">
+        <v>2</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="43">
+        <v>1</v>
+      </c>
+      <c r="R4" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="S4" s="23" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
-        <v>2</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="27">
-        <v>2</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H4" s="45">
+    <row r="5" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26">
+        <v>2</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="27">
+        <v>2</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="45">
         <v>5</v>
       </c>
-      <c r="I4" s="45">
-        <v>4</v>
-      </c>
-      <c r="J4" s="48">
-        <v>1</v>
-      </c>
-      <c r="K4" s="45">
-        <v>1</v>
-      </c>
-      <c r="L4" s="45">
-        <v>1</v>
-      </c>
-      <c r="M4" s="46">
-        <v>5</v>
-      </c>
-      <c r="N4" s="45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22">
-        <v>3</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="23">
-        <v>3</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="43">
-        <v>1</v>
-      </c>
-      <c r="I5" s="23">
-        <v>-999</v>
-      </c>
-      <c r="J5" s="47">
-        <v>2</v>
-      </c>
-      <c r="K5" s="23">
-        <v>-999</v>
-      </c>
-      <c r="L5" s="23">
-        <v>-999</v>
-      </c>
-      <c r="M5" s="43">
-        <v>2</v>
-      </c>
-      <c r="N5" s="43">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="48"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="45"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -1389,16 +1347,14 @@
       <c r="C6" s="27">
         <v>3</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" s="45">
-        <v>5</v>
-      </c>
+      <c r="D6" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="6"/>
       <c r="I6" s="45">
         <v>2</v>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="47">
         <v>2</v>
       </c>
       <c r="K6" s="45">
@@ -1407,1054 +1363,1114 @@
       <c r="L6" s="7">
         <v>-998</v>
       </c>
-      <c r="M6" s="45">
+      <c r="M6" s="43">
         <v>2</v>
       </c>
       <c r="N6" s="45">
         <v>-998</v>
       </c>
-      <c r="R6" s="27" t="s">
+    </row>
+    <row r="7" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="23">
+        <v>3</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="43">
+        <v>1</v>
+      </c>
+      <c r="N7" s="43"/>
+    </row>
+    <row r="8" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26">
+        <v>3</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="27">
+        <v>3</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="45">
+        <v>5</v>
+      </c>
+      <c r="J8" s="48"/>
+      <c r="M8" s="45"/>
+      <c r="R8" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="S6" s="27" t="s">
+      <c r="S8" s="27" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="H7" s="5">
-        <v>5</v>
-      </c>
-      <c r="I7" s="6">
-        <v>5</v>
-      </c>
-      <c r="J7" s="6">
-        <v>-998</v>
-      </c>
-      <c r="K7" s="6">
-        <v>5</v>
-      </c>
-      <c r="L7" s="6">
-        <v>-998</v>
-      </c>
-      <c r="M7" s="6">
-        <v>2</v>
-      </c>
-      <c r="N7" s="6">
-        <v>-998</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
-      </c>
-      <c r="S7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="H8" s="6">
-        <v>3</v>
-      </c>
-      <c r="I8" s="6">
-        <v>2</v>
-      </c>
-      <c r="J8" s="6">
-        <v>3</v>
-      </c>
-      <c r="K8" s="6">
-        <v>2</v>
-      </c>
-      <c r="L8" s="6">
-        <v>3</v>
-      </c>
-      <c r="M8" s="6">
-        <v>3</v>
-      </c>
-      <c r="N8" s="6">
-        <v>3</v>
-      </c>
-      <c r="R8" t="s">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>108</v>
       </c>
       <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="H9" s="6">
-        <v>-999</v>
+        <v>4</v>
+      </c>
+      <c r="H9" s="5">
+        <v>5</v>
       </c>
       <c r="I9" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" s="6">
-        <v>-999</v>
+        <v>-998</v>
       </c>
       <c r="K9" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" s="6">
-        <v>-999</v>
+        <v>-998</v>
       </c>
       <c r="M9" s="6">
-        <v>-999</v>
+        <v>2</v>
       </c>
       <c r="N9" s="6">
-        <v>-999</v>
+        <v>-998</v>
       </c>
       <c r="R9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S9" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>108</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="6">
-        <v>-999</v>
+        <v>2</v>
       </c>
       <c r="J10" s="6">
-        <v>-999</v>
+        <v>3</v>
       </c>
       <c r="K10" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L10" s="7">
-        <v>-999</v>
+        <v>2</v>
+      </c>
+      <c r="L10" s="6">
+        <v>3</v>
       </c>
       <c r="M10" s="6">
-        <v>-999</v>
+        <v>3</v>
       </c>
       <c r="N10" s="6">
-        <v>-999</v>
+        <v>3</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S10" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>108</v>
       </c>
       <c r="C11">
-        <v>8</v>
-      </c>
-      <c r="G11" s="2">
-        <v>999</v>
+        <v>6</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-999</v>
+      </c>
+      <c r="I11" s="6">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6">
+        <v>-999</v>
+      </c>
+      <c r="K11" s="6">
+        <v>3</v>
+      </c>
+      <c r="L11" s="6">
+        <v>-999</v>
+      </c>
+      <c r="M11" s="6">
+        <v>-999</v>
+      </c>
+      <c r="N11" s="6">
+        <v>-999</v>
       </c>
       <c r="R11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>108</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I12" s="6">
-        <v>0</v>
+        <v>-999</v>
       </c>
       <c r="J12" s="6">
-        <v>2</v>
+        <v>-999</v>
       </c>
       <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>1</v>
+        <v>-999</v>
+      </c>
+      <c r="L12" s="7">
+        <v>-999</v>
       </c>
       <c r="M12" s="6">
-        <v>1</v>
+        <v>-999</v>
       </c>
       <c r="N12" s="6">
-        <v>2</v>
+        <v>-999</v>
       </c>
       <c r="R12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>2</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>2</v>
-      </c>
-      <c r="M13" s="6">
-        <v>1</v>
-      </c>
-      <c r="N13" s="6">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-997</v>
       </c>
       <c r="R13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14">
-        <v>11</v>
-      </c>
-      <c r="O14">
-        <v>10000</v>
-      </c>
-      <c r="P14">
-        <v>20000</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>91</v>
+        <v>9</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>2</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1</v>
+      </c>
+      <c r="N14" s="6">
+        <v>2</v>
       </c>
       <c r="R14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15">
-        <v>12</v>
-      </c>
-      <c r="O15">
-        <v>20000</v>
-      </c>
-      <c r="P15">
-        <v>6000000</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>2</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>2</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1</v>
+      </c>
+      <c r="N15" s="6">
+        <v>2</v>
       </c>
       <c r="R15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S15" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16">
-        <v>13</v>
-      </c>
-      <c r="H16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="J16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N16" s="6">
-        <v>-999</v>
+        <v>11</v>
+      </c>
+      <c r="O16">
+        <v>10000</v>
+      </c>
+      <c r="P16">
+        <v>20000</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>91</v>
       </c>
       <c r="R16" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>108</v>
       </c>
       <c r="C17">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="O17">
+        <v>20000</v>
+      </c>
+      <c r="P17">
+        <v>6000000</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2">
-        <v>2</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="I18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="J18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="K18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="L18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="M18" s="6">
+        <v>-999</v>
+      </c>
+      <c r="N18" s="6">
+        <v>-999</v>
       </c>
       <c r="R18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19">
-        <v>16</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="S19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
         <v>110</v>
       </c>
       <c r="C20">
-        <v>17</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>11</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="S20" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>110</v>
       </c>
       <c r="C21">
-        <v>18</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>53</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>51</v>
+        <v>12</v>
+      </c>
+      <c r="S21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>110</v>
       </c>
       <c r="C22">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="R22" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>110</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="R23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
+        <v>110</v>
+      </c>
+      <c r="C24">
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
+        <v>110</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
         <v>111</v>
       </c>
-      <c r="C27">
-        <v>22</v>
-      </c>
-      <c r="G27" s="55">
-        <v>4</v>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
       </c>
       <c r="R27" t="s">
-        <v>68</v>
-      </c>
-      <c r="S27" t="s">
-        <v>69</v>
+        <v>58</v>
+      </c>
+      <c r="S27" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28">
-        <v>23</v>
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R28" t="s">
-        <v>70</v>
-      </c>
-      <c r="S28" t="s">
-        <v>10</v>
+        <v>59</v>
+      </c>
+      <c r="S28" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G29" s="55">
         <v>4</v>
       </c>
       <c r="R29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S29" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
         <v>112</v>
       </c>
       <c r="C30">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>112</v>
       </c>
       <c r="C31">
-        <v>26</v>
-      </c>
-      <c r="G31" s="4">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="G31" s="55">
+        <v>4</v>
       </c>
       <c r="R31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S31" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="S32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33">
-        <v>28</v>
-      </c>
-      <c r="G33" s="2">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2</v>
       </c>
       <c r="R33" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="S33" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
       </c>
       <c r="C34">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G34">
         <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S34" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
       <c r="C35">
-        <v>30</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3</v>
       </c>
       <c r="R35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S35" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
         <v>113</v>
       </c>
       <c r="C36">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G36">
         <v>5</v>
       </c>
       <c r="R36" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="S36" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C37">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C38">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G38">
         <v>5</v>
       </c>
       <c r="R38" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="S38" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
         <v>114</v>
       </c>
       <c r="C39">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="R39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
         <v>114</v>
       </c>
       <c r="C40">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S40" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C41">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="R41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C42">
-        <v>37</v>
-      </c>
-      <c r="O42">
-        <v>6000</v>
-      </c>
-      <c r="P42">
-        <v>8000</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>89</v>
+        <v>35</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S42" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43">
-        <v>38</v>
-      </c>
-      <c r="O43">
-        <v>50000</v>
-      </c>
-      <c r="P43">
-        <v>10000</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
       </c>
       <c r="R43" t="s">
-        <v>15</v>
-      </c>
-      <c r="S43" s="8" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="S43" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O44">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="P44">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="Q44" t="s">
         <v>89</v>
       </c>
       <c r="R44" t="s">
-        <v>16</v>
-      </c>
-      <c r="S44" s="8" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="S44" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O45">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="P45">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="Q45" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O46">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="P46">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="Q46" t="s">
         <v>89</v>
       </c>
       <c r="R46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="O47">
+        <v>500</v>
+      </c>
+      <c r="P47">
+        <v>500</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>89</v>
       </c>
       <c r="R47" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="O48">
+        <v>2000</v>
+      </c>
+      <c r="P48">
+        <v>3000</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>89</v>
       </c>
       <c r="R48" t="s">
-        <v>99</v>
+        <v>18</v>
+      </c>
+      <c r="S48" s="8" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49">
+        <v>42</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>89</v>
+      </c>
+      <c r="R49" t="s">
+        <v>98</v>
+      </c>
+      <c r="S49" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50">
+        <v>43</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>89</v>
+      </c>
+      <c r="R50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>46</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51">
         <v>44</v>
       </c>
-      <c r="G49">
+      <c r="G51">
         <v>5</v>
       </c>
-      <c r="R49" t="s">
+      <c r="R51" t="s">
         <v>100</v>
       </c>
-      <c r="S49" s="8" t="s">
+      <c r="S51" s="8" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52">
+        <v>45</v>
+      </c>
+      <c r="G52">
+        <v>-999</v>
+      </c>
+      <c r="R52" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2466,7 +2482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FABCB46-76B1-45AE-9EC3-251841A9849E}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -2496,13 +2512,13 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -2688,8 +2704,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
-        <v>159</v>
+      <c r="F6" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="H6">
         <v>-999</v>
@@ -2721,10 +2737,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7">
-        <v>-999</v>
+        <v>162</v>
       </c>
       <c r="I7" s="6">
         <v>1</v>
@@ -2746,10 +2759,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8">
-        <v>-999</v>
+        <v>163</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -2924,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="9">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="R13" t="s">
         <v>38</v>
@@ -3695,6 +3705,9 @@
       <c r="C48">
         <v>43</v>
       </c>
+      <c r="Q48" t="s">
+        <v>175</v>
+      </c>
       <c r="R48" t="s">
         <v>99</v>
       </c>
@@ -3717,6 +3730,23 @@
       </c>
       <c r="S49" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50">
+        <v>45</v>
+      </c>
+      <c r="G50">
+        <v>-999</v>
+      </c>
+      <c r="R50" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3727,7 +3757,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B51270F-FFBC-4EA1-B493-B161BDCA8EC1}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -3741,13 +3771,13 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -3857,8 +3887,8 @@
       <c r="C4" s="23">
         <v>3</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>159</v>
+      <c r="F4" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="H4" s="23">
         <v>-999</v>
@@ -3889,7 +3919,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -3908,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -3931,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M7" s="28">
         <v>999</v>
@@ -4974,6 +5004,9 @@
       <c r="C49">
         <v>43</v>
       </c>
+      <c r="Q49" t="s">
+        <v>175</v>
+      </c>
       <c r="R49" t="s">
         <v>99</v>
       </c>
@@ -4996,6 +5029,23 @@
       </c>
       <c r="S50" s="1" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51">
+        <v>45</v>
+      </c>
+      <c r="G51">
+        <v>-999</v>
+      </c>
+      <c r="R51" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5005,7 +5055,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD628265-A169-414F-BB6E-7496B95E445F}">
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="12.5546875" customWidth="1"/>
@@ -5022,13 +5072,13 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -5752,6 +5802,9 @@
       <c r="C26">
         <v>23</v>
       </c>
+      <c r="G26" s="6">
+        <v>-999</v>
+      </c>
       <c r="R26" t="s">
         <v>70</v>
       </c>
@@ -5789,6 +5842,9 @@
       <c r="C28">
         <v>25</v>
       </c>
+      <c r="G28" s="6">
+        <v>-999</v>
+      </c>
       <c r="R28" t="s">
         <v>72</v>
       </c>
@@ -6031,6 +6087,9 @@
         <v>37</v>
       </c>
       <c r="O40" s="11"/>
+      <c r="Q40" t="s">
+        <v>175</v>
+      </c>
       <c r="R40" t="s">
         <v>88</v>
       </c>
@@ -6098,6 +6157,9 @@
       <c r="C43">
         <v>40</v>
       </c>
+      <c r="Q43" t="s">
+        <v>175</v>
+      </c>
       <c r="R43" t="s">
         <v>17</v>
       </c>
@@ -6115,6 +6177,9 @@
       <c r="C44">
         <v>41</v>
       </c>
+      <c r="Q44" t="s">
+        <v>175</v>
+      </c>
       <c r="R44" t="s">
         <v>18</v>
       </c>
@@ -6132,6 +6197,9 @@
       <c r="C45">
         <v>42</v>
       </c>
+      <c r="Q45" t="s">
+        <v>175</v>
+      </c>
       <c r="R45" t="s">
         <v>98</v>
       </c>
@@ -6149,6 +6217,9 @@
       <c r="C46">
         <v>43</v>
       </c>
+      <c r="Q46" t="s">
+        <v>175</v>
+      </c>
       <c r="R46" t="s">
         <v>99</v>
       </c>
@@ -6171,6 +6242,23 @@
       </c>
       <c r="S47" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48">
+        <v>45</v>
+      </c>
+      <c r="G48">
+        <v>-999</v>
+      </c>
+      <c r="R48" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6180,7 +6268,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26691114-F8EB-4EEB-B292-06EA58F9BDCC}">
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -6194,13 +6282,13 @@
         <v>64</v>
       </c>
       <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" t="s">
-        <v>162</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -6266,8 +6354,8 @@
       <c r="C3" s="23">
         <v>2</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>159</v>
+      <c r="F3" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="H3" s="29" t="s">
         <v>131</v>
@@ -6303,7 +6391,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -6320,7 +6408,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -6337,7 +6425,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -6354,7 +6442,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6371,7 +6459,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I8" s="27">
         <v>2</v>
@@ -6387,11 +6475,11 @@
       <c r="C9" s="23">
         <v>3</v>
       </c>
-      <c r="F9" s="23" t="s">
-        <v>159</v>
+      <c r="F9" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="H9" s="30">
-        <v>999</v>
+        <v>-997</v>
       </c>
       <c r="I9" s="29"/>
       <c r="J9" s="29">
@@ -6424,10 +6512,10 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H10" s="10"/>
-      <c r="I10" s="58">
+      <c r="I10" s="10">
         <v>4</v>
       </c>
       <c r="J10" s="10"/>
@@ -6447,10 +6535,10 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11" s="10"/>
-      <c r="I11" s="58">
+      <c r="I11" s="10">
         <v>4</v>
       </c>
       <c r="J11" s="10"/>
@@ -6470,7 +6558,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
@@ -6493,7 +6581,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="10">
@@ -6516,7 +6604,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="31">
@@ -6811,8 +6899,8 @@
       <c r="C24" s="23">
         <v>13</v>
       </c>
-      <c r="F24" s="23" t="s">
-        <v>159</v>
+      <c r="F24" s="33" t="s">
+        <v>169</v>
       </c>
       <c r="H24" s="29">
         <v>2</v>
@@ -6848,7 +6936,7 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -6868,7 +6956,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I26" s="27">
         <v>2</v>
@@ -7089,6 +7177,9 @@
       <c r="C38">
         <v>23</v>
       </c>
+      <c r="G38" s="6">
+        <v>-999</v>
+      </c>
       <c r="R38" t="s">
         <v>70</v>
       </c>
@@ -7120,6 +7211,9 @@
       <c r="C40">
         <v>25</v>
       </c>
+      <c r="G40" s="6">
+        <v>-999</v>
+      </c>
       <c r="R40" t="s">
         <v>72</v>
       </c>
@@ -7328,6 +7422,9 @@
         <v>37</v>
       </c>
       <c r="O52" s="11"/>
+      <c r="Q52" t="s">
+        <v>175</v>
+      </c>
       <c r="R52" t="s">
         <v>88</v>
       </c>
@@ -7411,6 +7508,9 @@
       <c r="C56">
         <v>41</v>
       </c>
+      <c r="Q56" t="s">
+        <v>175</v>
+      </c>
       <c r="R56" t="s">
         <v>18</v>
       </c>
@@ -7448,6 +7548,9 @@
       <c r="C58">
         <v>43</v>
       </c>
+      <c r="Q58" t="s">
+        <v>175</v>
+      </c>
       <c r="R58" t="s">
         <v>99</v>
       </c>
@@ -7467,6 +7570,23 @@
       </c>
       <c r="R59" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>47</v>
+      </c>
+      <c r="B60" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60">
+        <v>45</v>
+      </c>
+      <c r="G60">
+        <v>-999</v>
+      </c>
+      <c r="R60" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -7495,13 +7615,13 @@
         <v>64</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>2</v>
@@ -7574,7 +7694,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H3" s="34" t="s">
         <v>136</v>
@@ -7613,7 +7733,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M4" s="14">
         <v>4</v>
@@ -7636,7 +7756,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M5" s="57">
         <v>1</v>
@@ -7659,7 +7779,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
@@ -7698,7 +7818,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I7" s="14">
         <v>2</v>
@@ -7715,9 +7835,9 @@
         <v>3</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="59">
+        <v>171</v>
+      </c>
+      <c r="I8" s="37">
         <v>4</v>
       </c>
     </row>
@@ -8109,7 +8229,7 @@
         <v>-999</v>
       </c>
       <c r="N20" s="16">
-        <v>999</v>
+        <v>4</v>
       </c>
       <c r="R20" s="14" t="s">
         <v>47</v>
@@ -8488,7 +8608,7 @@
       <c r="C39" s="14">
         <v>32</v>
       </c>
-      <c r="G39" s="60">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
       <c r="R39" s="14" t="s">
@@ -8508,7 +8628,7 @@
       <c r="C40" s="14">
         <v>33</v>
       </c>
-      <c r="G40" s="60">
+      <c r="G40" s="14">
         <v>5</v>
       </c>
       <c r="R40" s="14" t="s">
@@ -8528,7 +8648,7 @@
       <c r="C41" s="14">
         <v>34</v>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="14">
         <v>5</v>
       </c>
       <c r="R41" s="14" t="s">
@@ -8548,7 +8668,7 @@
       <c r="C42" s="14">
         <v>35</v>
       </c>
-      <c r="G42" s="60">
+      <c r="G42" s="14">
         <v>2</v>
       </c>
       <c r="R42" s="14" t="s">
@@ -8568,7 +8688,6 @@
       <c r="C43" s="14">
         <v>36</v>
       </c>
-      <c r="G43" s="60"/>
       <c r="O43" s="17">
         <v>140</v>
       </c>
@@ -8673,6 +8792,9 @@
       <c r="C47" s="14">
         <v>40</v>
       </c>
+      <c r="Q47" t="s">
+        <v>175</v>
+      </c>
       <c r="R47" s="14" t="s">
         <v>17</v>
       </c>
@@ -8690,6 +8812,9 @@
       <c r="C48" s="14">
         <v>41</v>
       </c>
+      <c r="Q48" t="s">
+        <v>175</v>
+      </c>
       <c r="R48" s="14" t="s">
         <v>18</v>
       </c>
@@ -8707,7 +8832,6 @@
       <c r="C49" s="14">
         <v>42</v>
       </c>
-      <c r="G49" s="60"/>
       <c r="O49" s="14">
         <v>0</v>
       </c>
@@ -8734,7 +8858,9 @@
       <c r="C50" s="14">
         <v>43</v>
       </c>
-      <c r="G50" s="60"/>
+      <c r="Q50" t="s">
+        <v>175</v>
+      </c>
       <c r="R50" s="14" t="s">
         <v>99</v>
       </c>
@@ -8749,7 +8875,7 @@
       <c r="C51" s="14">
         <v>44</v>
       </c>
-      <c r="G51" s="60">
+      <c r="G51" s="14">
         <v>5</v>
       </c>
       <c r="R51" s="14" t="s">
@@ -8760,7 +8886,34 @@
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G52" s="60"/>
+      <c r="A52">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52">
+        <v>45</v>
+      </c>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52">
+        <v>-999</v>
+      </c>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52" t="s">
+        <v>177</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8769,14 +8922,17 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40DC07B-E25F-4A7F-9959-D54B043EB346}">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="8.88671875" style="14"/>
     <col min="6" max="6" width="21.88671875" style="14" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="14" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" style="14" customWidth="1"/>
-    <col min="9" max="16" width="8.88671875" style="14"/>
+    <col min="9" max="12" width="8.88671875" style="14"/>
+    <col min="13" max="13" width="14.44140625" style="14" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" style="14" customWidth="1"/>
+    <col min="15" max="16" width="8.88671875" style="14"/>
     <col min="17" max="17" width="12.5546875" style="14" customWidth="1"/>
     <col min="18" max="16384" width="8.88671875" style="14"/>
   </cols>
@@ -8792,13 +8948,13 @@
         <v>64</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>2</v>
@@ -8871,7 +9027,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H3" s="34">
         <v>4.5</v>
@@ -8885,13 +9041,13 @@
       <c r="K3" s="39">
         <v>1</v>
       </c>
-      <c r="L3" s="61">
+      <c r="L3" s="34">
         <v>4</v>
       </c>
-      <c r="M3" s="61">
-        <v>3</v>
-      </c>
-      <c r="N3" s="61">
+      <c r="M3" s="34">
+        <v>3</v>
+      </c>
+      <c r="N3" s="34">
         <v>1</v>
       </c>
       <c r="R3" s="33" t="s">
@@ -8909,7 +9065,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I4" s="14">
         <v>1</v>
@@ -8926,7 +9082,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I5" s="37">
         <v>2</v>
@@ -8946,7 +9102,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="34">
         <v>-999</v>
@@ -8985,7 +9141,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15">
@@ -9008,7 +9164,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H8" s="40"/>
       <c r="I8" s="40">
@@ -9046,10 +9202,10 @@
         <v>1</v>
       </c>
       <c r="M9" s="41">
-        <v>999</v>
+        <v>-998</v>
       </c>
       <c r="N9" s="41">
-        <v>999</v>
+        <v>-998</v>
       </c>
       <c r="R9" s="14" t="s">
         <v>29</v>
@@ -9069,7 +9225,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H10" s="34">
         <v>3</v>
@@ -9104,7 +9260,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15">
@@ -9127,7 +9283,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I12" s="37">
         <v>1</v>
@@ -9470,7 +9626,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G23" s="52">
         <v>1</v>
@@ -9493,7 +9649,7 @@
         <v>16</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G24" s="53">
         <v>0</v>
@@ -10112,6 +10268,9 @@
       <c r="C53" s="14">
         <v>43</v>
       </c>
+      <c r="Q53" t="s">
+        <v>175</v>
+      </c>
       <c r="R53" s="14" t="s">
         <v>99</v>
       </c>
@@ -10129,11 +10288,42 @@
       <c r="G54" s="37">
         <v>5</v>
       </c>
+      <c r="Q54"/>
       <c r="R54" s="37" t="s">
         <v>100</v>
       </c>
       <c r="S54" s="37" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55">
+        <v>45</v>
+      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55">
+        <v>-999</v>
+      </c>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D8C614-C522-4B20-BF5F-04C2889480D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7C1707-E19D-4CBA-9322-63DD8A9CCCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I_1" sheetId="1" r:id="rId1"/>
@@ -1424,22 +1424,22 @@
         <v>4</v>
       </c>
       <c r="H9" s="5">
-        <v>5</v>
+        <v>-997</v>
       </c>
       <c r="I9" s="6">
-        <v>5</v>
+        <v>-997</v>
       </c>
       <c r="J9" s="6">
         <v>-998</v>
       </c>
       <c r="K9" s="6">
-        <v>5</v>
+        <v>-997</v>
       </c>
       <c r="L9" s="6">
         <v>-998</v>
       </c>
       <c r="M9" s="6">
-        <v>2</v>
+        <v>-997</v>
       </c>
       <c r="N9" s="6">
         <v>-998</v>
@@ -6486,7 +6486,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="29">
-        <v>-999</v>
+        <v>-998</v>
       </c>
       <c r="L9" s="29">
         <v>3</v>
@@ -6495,7 +6495,7 @@
         <v>133</v>
       </c>
       <c r="N9" s="29">
-        <v>-999</v>
+        <v>-998</v>
       </c>
       <c r="R9" s="23" t="s">
         <v>28</v>

--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7C1707-E19D-4CBA-9322-63DD8A9CCCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C417E4-DA20-4C63-A6D1-57048F566C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="179">
   <si>
     <t>If the [extreme event] happen, how likely are you to go out fishing?</t>
   </si>
@@ -573,9 +573,6 @@
     <t>NorthSea</t>
   </si>
   <si>
-    <t>salmon_whitefish</t>
-  </si>
-  <si>
     <t>rod</t>
   </si>
   <si>
@@ -589,6 +586,12 @@
   </si>
   <si>
     <t>addit</t>
+  </si>
+  <si>
+    <t>icefishing</t>
+  </si>
+  <si>
+    <t>whitefish</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
@@ -1305,7 +1308,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H4" s="43">
         <v>1</v>
@@ -1328,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H5" s="45">
         <v>5</v>
@@ -1381,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H7" s="43">
         <v>1</v>
@@ -1399,7 +1402,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H8" s="45">
         <v>5</v>
@@ -1595,9 +1598,10 @@
       <c r="C14">
         <v>9</v>
       </c>
-      <c r="H14" s="6">
-        <v>1</v>
-      </c>
+      <c r="D14" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="6"/>
       <c r="I14" s="6">
         <v>0</v>
       </c>
@@ -1625,852 +1629,869 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>2</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>2</v>
-      </c>
-      <c r="M15" s="6">
-        <v>1</v>
-      </c>
-      <c r="N15" s="6">
-        <v>2</v>
-      </c>
-      <c r="R15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S15" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16">
-        <v>11</v>
-      </c>
-      <c r="O16">
-        <v>10000</v>
-      </c>
-      <c r="P16">
-        <v>20000</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>2</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>2</v>
+      </c>
+      <c r="M16" s="6">
+        <v>1</v>
+      </c>
+      <c r="N16" s="6">
+        <v>2</v>
       </c>
       <c r="R16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S16" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O17">
+        <v>10000</v>
+      </c>
+      <c r="P17">
         <v>20000</v>
-      </c>
-      <c r="P17">
-        <v>6000000</v>
       </c>
       <c r="Q17" t="s">
         <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>108</v>
       </c>
       <c r="C18">
-        <v>13</v>
-      </c>
-      <c r="H18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="J18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N18" s="6">
-        <v>-999</v>
+        <v>12</v>
+      </c>
+      <c r="O18">
+        <v>20000</v>
+      </c>
+      <c r="P18">
+        <v>6000000</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>91</v>
       </c>
       <c r="R18" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>108</v>
       </c>
       <c r="C19">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="I19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="J19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="K19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="L19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="M19" s="6">
+        <v>-999</v>
+      </c>
+      <c r="N19" s="6">
+        <v>-999</v>
       </c>
       <c r="R19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20">
-        <v>15</v>
-      </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2">
-        <v>2</v>
-      </c>
-      <c r="L20" s="2">
-        <v>1</v>
-      </c>
-      <c r="M20" s="2">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2">
+        <v>14</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
         <v>110</v>
       </c>
       <c r="C21">
-        <v>16</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="S21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
         <v>110</v>
       </c>
       <c r="C22">
-        <v>17</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>11</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="S22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
         <v>110</v>
       </c>
       <c r="C23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="R23" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>110</v>
       </c>
       <c r="C24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="R24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>110</v>
       </c>
       <c r="C25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="R25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
+        <v>110</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
         <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="R27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>111</v>
       </c>
-      <c r="C29">
-        <v>22</v>
-      </c>
-      <c r="G29" s="55">
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29">
         <v>4</v>
       </c>
       <c r="R29" t="s">
-        <v>68</v>
-      </c>
-      <c r="S29" t="s">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="S29" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C30">
-        <v>23</v>
-      </c>
-      <c r="G30">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="G30" s="55">
+        <v>4</v>
       </c>
       <c r="R30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S30" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
         <v>112</v>
       </c>
       <c r="C31">
-        <v>24</v>
-      </c>
-      <c r="G31" s="55">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
       </c>
       <c r="R31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
         <v>112</v>
       </c>
       <c r="C32">
-        <v>25</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="G32" s="55">
+        <v>4</v>
       </c>
       <c r="R32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
         <v>112</v>
       </c>
       <c r="C33">
-        <v>26</v>
-      </c>
-      <c r="G33" s="4">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C34">
-        <v>27</v>
-      </c>
-      <c r="G34">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2</v>
       </c>
       <c r="R34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="S34" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
         <v>113</v>
       </c>
       <c r="C35">
-        <v>28</v>
-      </c>
-      <c r="G35" s="2">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
       </c>
       <c r="R35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S35" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
         <v>113</v>
       </c>
       <c r="C36">
-        <v>29</v>
-      </c>
-      <c r="G36">
-        <v>5</v>
+        <v>28</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3</v>
       </c>
       <c r="R36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>113</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
         <v>113</v>
       </c>
       <c r="C38">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="S38" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="R39" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="S39" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>114</v>
       </c>
       <c r="C40">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>5</v>
       </c>
       <c r="R40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S40" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
         <v>114</v>
       </c>
       <c r="C41">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G41">
         <v>5</v>
       </c>
       <c r="R41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S41" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
         <v>114</v>
       </c>
       <c r="C42">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S42" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S43" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44">
-        <v>37</v>
-      </c>
-      <c r="O44">
-        <v>6000</v>
-      </c>
-      <c r="P44">
-        <v>8000</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>89</v>
+        <v>36</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
       </c>
       <c r="R44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O45">
-        <v>50000</v>
+        <v>6000</v>
       </c>
       <c r="P45">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="Q45" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R45" t="s">
-        <v>15</v>
-      </c>
-      <c r="S45" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="S45" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O46">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="P46">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="Q46" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O47">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="P47">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Q47" t="s">
         <v>89</v>
       </c>
       <c r="R47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O48">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="P48">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="Q48" t="s">
         <v>89</v>
       </c>
       <c r="R48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S48" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="O49">
+        <v>2000</v>
+      </c>
+      <c r="P49">
+        <v>3000</v>
       </c>
       <c r="Q49" t="s">
         <v>89</v>
       </c>
       <c r="R49" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="S49" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q50" t="s">
         <v>89</v>
       </c>
       <c r="R50" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51">
-        <v>44</v>
-      </c>
-      <c r="G51">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>89</v>
       </c>
       <c r="R51" t="s">
-        <v>100</v>
-      </c>
-      <c r="S51" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52">
+        <v>46</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52">
+        <v>44</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+      <c r="R52" t="s">
+        <v>100</v>
+      </c>
+      <c r="S52" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>47</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53">
+        <v>45</v>
+      </c>
+      <c r="G53">
+        <v>-999</v>
+      </c>
+      <c r="R53" t="s">
         <v>176</v>
-      </c>
-      <c r="C52">
-        <v>45</v>
-      </c>
-      <c r="G52">
-        <v>-999</v>
-      </c>
-      <c r="R52" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3706,7 +3727,7 @@
         <v>43</v>
       </c>
       <c r="Q48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R48" t="s">
         <v>99</v>
@@ -3737,7 +3758,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C50">
         <v>45</v>
@@ -3746,7 +3767,7 @@
         <v>-999</v>
       </c>
       <c r="R50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -5005,7 +5026,7 @@
         <v>43</v>
       </c>
       <c r="Q49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R49" t="s">
         <v>99</v>
@@ -5036,7 +5057,7 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51">
         <v>45</v>
@@ -5045,7 +5066,7 @@
         <v>-999</v>
       </c>
       <c r="R51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -6088,7 +6109,7 @@
       </c>
       <c r="O40" s="11"/>
       <c r="Q40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R40" t="s">
         <v>88</v>
@@ -6158,7 +6179,7 @@
         <v>40</v>
       </c>
       <c r="Q43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R43" t="s">
         <v>17</v>
@@ -6178,7 +6199,7 @@
         <v>41</v>
       </c>
       <c r="Q44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R44" t="s">
         <v>18</v>
@@ -6198,7 +6219,7 @@
         <v>42</v>
       </c>
       <c r="Q45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R45" t="s">
         <v>98</v>
@@ -6218,7 +6239,7 @@
         <v>43</v>
       </c>
       <c r="Q46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R46" t="s">
         <v>99</v>
@@ -6249,7 +6270,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C48">
         <v>45</v>
@@ -6258,7 +6279,7 @@
         <v>-999</v>
       </c>
       <c r="R48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -7423,7 +7444,7 @@
       </c>
       <c r="O52" s="11"/>
       <c r="Q52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R52" t="s">
         <v>88</v>
@@ -7509,7 +7530,7 @@
         <v>41</v>
       </c>
       <c r="Q56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R56" t="s">
         <v>18</v>
@@ -7549,7 +7570,7 @@
         <v>43</v>
       </c>
       <c r="Q58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R58" t="s">
         <v>99</v>
@@ -7577,7 +7598,7 @@
         <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C60">
         <v>45</v>
@@ -7586,7 +7607,7 @@
         <v>-999</v>
       </c>
       <c r="R60" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -8793,7 +8814,7 @@
         <v>40</v>
       </c>
       <c r="Q47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R47" s="14" t="s">
         <v>17</v>
@@ -8813,7 +8834,7 @@
         <v>41</v>
       </c>
       <c r="Q48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R48" s="14" t="s">
         <v>18</v>
@@ -8859,7 +8880,7 @@
         <v>43</v>
       </c>
       <c r="Q50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R50" s="14" t="s">
         <v>99</v>
@@ -8890,7 +8911,7 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C52">
         <v>45</v>
@@ -8912,7 +8933,7 @@
       <c r="P52"/>
       <c r="Q52"/>
       <c r="R52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -8922,10 +8943,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40DC07B-E25F-4A7F-9959-D54B043EB346}">
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="8.88671875" style="14"/>
+    <col min="1" max="3" width="8.88671875" style="14"/>
+    <col min="4" max="4" width="12.44140625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="14"/>
     <col min="6" max="6" width="21.88671875" style="14" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="14" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" style="14" customWidth="1"/>
@@ -9260,7 +9283,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15">
@@ -9272,82 +9295,67 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
     </row>
-    <row r="12" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="35">
         <v>5</v>
       </c>
-      <c r="B12" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="37">
+      <c r="B12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="14">
         <v>5</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36">
+        <v>5</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="37">
+        <v>5</v>
+      </c>
+      <c r="F13" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="I12" s="37">
-        <v>1</v>
-      </c>
-      <c r="R12" s="37" t="s">
+      <c r="I13" s="37">
+        <v>1</v>
+      </c>
+      <c r="R13" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="S12" s="37" t="s">
+      <c r="S13" s="37" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="14">
-        <v>6</v>
-      </c>
-      <c r="H13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="I13" s="15">
-        <v>3</v>
-      </c>
-      <c r="J13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="N13" s="15">
-        <v>-999</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C14" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="15">
         <v>-999</v>
       </c>
       <c r="I14" s="15">
-        <v>-999</v>
+        <v>3</v>
       </c>
       <c r="J14" s="15">
         <v>-999</v>
@@ -9359,89 +9367,87 @@
         <v>-999</v>
       </c>
       <c r="M14" s="15">
-        <v>3.5</v>
+        <v>-999</v>
       </c>
       <c r="N14" s="15">
-        <v>3.5</v>
+        <v>-999</v>
       </c>
       <c r="R14" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C15" s="14">
-        <v>8</v>
-      </c>
-      <c r="G15" s="51">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-999</v>
+      </c>
+      <c r="I15" s="15">
+        <v>-999</v>
+      </c>
+      <c r="J15" s="15">
+        <v>-999</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-999</v>
+      </c>
+      <c r="L15" s="15">
+        <v>-999</v>
+      </c>
+      <c r="M15" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="N15" s="15">
+        <v>3.5</v>
       </c>
       <c r="R15" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
+        <v>8</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="14">
+        <v>8</v>
+      </c>
+      <c r="G16" s="51">
+        <v>2</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B17" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="14">
         <v>9</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="14">
-        <v>9</v>
-      </c>
-      <c r="H16" s="15">
-        <v>2</v>
-      </c>
-      <c r="I16" s="15">
-        <v>0</v>
-      </c>
-      <c r="J16" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K16" s="15">
-        <v>0</v>
-      </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15">
-        <v>2</v>
-      </c>
-      <c r="N16" s="15">
-        <v>2</v>
-      </c>
-      <c r="R16" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
-        <v>10</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="14">
-        <v>10</v>
-      </c>
-      <c r="H17" s="15">
-        <v>0</v>
-      </c>
+      <c r="D17" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="51"/>
       <c r="I17" s="15">
         <v>0</v>
       </c>
@@ -9449,881 +9455,934 @@
         <v>-999</v>
       </c>
       <c r="K17" s="15">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="15">
         <v>2</v>
       </c>
       <c r="R17" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S17" s="14" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
-        <v>11</v>
-      </c>
       <c r="B18" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="14">
-        <v>11</v>
-      </c>
-      <c r="O18" s="15">
-        <v>1000</v>
-      </c>
-      <c r="P18" s="15">
-        <v>50000</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="S18" s="14" t="s">
-        <v>42</v>
+        <v>9</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="51"/>
+      <c r="H18" s="15">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
-      </c>
-      <c r="O19" s="15">
-        <v>50000</v>
-      </c>
-      <c r="P19" s="15">
-        <v>100000</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15">
+        <v>-999</v>
+      </c>
+      <c r="K19" s="15">
+        <v>1</v>
+      </c>
+      <c r="L19" s="16">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15">
+        <v>1</v>
+      </c>
+      <c r="N19" s="15">
+        <v>2</v>
       </c>
       <c r="R19" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S19" s="14" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
-      </c>
-      <c r="H20" s="15">
-        <v>2</v>
-      </c>
-      <c r="I20" s="15">
-        <v>1</v>
-      </c>
-      <c r="J20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L20" s="15">
-        <v>0</v>
-      </c>
-      <c r="M20" s="21">
-        <v>1</v>
-      </c>
-      <c r="N20" s="15">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="O20" s="15">
+        <v>1000</v>
+      </c>
+      <c r="P20" s="15">
+        <v>50000</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="R20" s="14" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="S20" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C21" s="14">
-        <v>14</v>
-      </c>
-      <c r="G21" s="51">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="O21" s="15">
+        <v>50000</v>
+      </c>
+      <c r="P21" s="15">
+        <v>100000</v>
+      </c>
+      <c r="Q21" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="R21" s="14" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="S21" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
+        <v>13</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="14">
+        <v>13</v>
+      </c>
+      <c r="H22" s="15">
+        <v>2</v>
+      </c>
+      <c r="I22" s="15">
+        <v>1</v>
+      </c>
+      <c r="J22" s="15">
+        <v>-999</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-999</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="21">
+        <v>1</v>
+      </c>
+      <c r="N22" s="15">
+        <v>2</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="S22" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <v>14</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="14">
+        <v>14</v>
+      </c>
+      <c r="G23" s="51">
+        <v>2</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
         <v>15</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B24" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C24" s="14">
         <v>15</v>
       </c>
-      <c r="H22" s="15">
-        <v>1</v>
-      </c>
-      <c r="I22" s="15">
-        <v>2</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="H24" s="15">
+        <v>1</v>
+      </c>
+      <c r="I24" s="15">
+        <v>2</v>
+      </c>
+      <c r="J24" s="15">
         <v>4</v>
       </c>
-      <c r="K22" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L22" s="15">
-        <v>1</v>
-      </c>
-      <c r="M22" s="15">
+      <c r="K24" s="15">
+        <v>-999</v>
+      </c>
+      <c r="L24" s="15">
+        <v>1</v>
+      </c>
+      <c r="M24" s="15">
         <v>4</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N24" s="15">
         <v>4</v>
       </c>
-      <c r="R22" s="14" t="s">
+      <c r="R24" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S24" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32">
+    <row r="25" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="32">
         <v>16</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B25" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C25" s="33">
         <v>16</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F25" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="G23" s="52">
-        <v>1</v>
-      </c>
-      <c r="R23" s="33" t="s">
+      <c r="G25" s="52">
+        <v>1</v>
+      </c>
+      <c r="R25" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S25" s="33" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36">
+    <row r="26" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="36">
         <v>16</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B26" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C26" s="37">
         <v>16</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F26" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="53">
+      <c r="G26" s="53">
         <v>0</v>
       </c>
-      <c r="R24" s="37" t="s">
+      <c r="R26" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="S24" s="37" t="s">
+      <c r="S26" s="37" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
-        <v>17</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="14">
-        <v>17</v>
-      </c>
-      <c r="G25" s="51">
-        <v>0</v>
-      </c>
-      <c r="R25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="S25" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
-        <v>18</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="14">
-        <v>18</v>
-      </c>
-      <c r="G26" s="51">
-        <v>1</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="S26" s="14" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C27" s="14">
-        <v>19</v>
-      </c>
-      <c r="G27" s="19">
-        <v>999</v>
+        <v>17</v>
+      </c>
+      <c r="G27" s="51">
+        <v>0</v>
       </c>
       <c r="R27" s="14" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="S27" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C28" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G28" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="S28" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="51">
-        <v>1</v>
+        <v>110</v>
+      </c>
+      <c r="C29" s="14">
+        <v>19</v>
+      </c>
+      <c r="G29" s="19">
+        <v>999</v>
       </c>
       <c r="R29" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S29" s="14" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>66</v>
+        <v>110</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
       </c>
       <c r="G30" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R30" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S30" s="14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>111</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G31" s="51">
         <v>1</v>
       </c>
       <c r="R31" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="S31" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="14">
-        <v>22</v>
+      <c r="C32" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="G32" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" s="14" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="S32" s="14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="14">
-        <v>23</v>
-      </c>
-      <c r="G33" s="14">
-        <v>3</v>
+        <v>111</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="51">
+        <v>1</v>
       </c>
       <c r="R33" s="14" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="S33" s="14" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C34" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G34" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R34" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S34" s="14" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>112</v>
       </c>
       <c r="C35" s="14">
-        <v>25</v>
-      </c>
-      <c r="G35" s="38">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="G35" s="14">
+        <v>3</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S35" s="14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>112</v>
       </c>
       <c r="C36" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G36" s="51">
         <v>4</v>
       </c>
       <c r="R36" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S36" s="14" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C37" s="14">
-        <v>27</v>
-      </c>
-      <c r="G37" s="14">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="G37" s="38">
+        <v>2</v>
       </c>
       <c r="R37" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="S37" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38" s="51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R38" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="S38" s="14" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C39" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G39" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S39" s="14" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C40" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G40" s="51">
         <v>5</v>
       </c>
       <c r="R40" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C41" s="14">
-        <v>31</v>
-      </c>
-      <c r="G41" s="20">
-        <v>3</v>
+        <v>29</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
       </c>
       <c r="R41" s="14" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="S41" s="14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="14">
-        <v>32</v>
-      </c>
-      <c r="G42" s="20">
+        <v>30</v>
+      </c>
+      <c r="G42" s="51">
         <v>5</v>
       </c>
       <c r="R42" s="14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S42" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C43" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G43" s="20">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R43" s="14" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="S43" s="14" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>114</v>
       </c>
       <c r="C44" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G44" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R44" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S44" s="14" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>114</v>
       </c>
       <c r="C45" s="14">
+        <v>33</v>
+      </c>
+      <c r="G45" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="R45" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="S45" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" s="14">
+        <v>36</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="14">
+        <v>34</v>
+      </c>
+      <c r="G46" s="20">
+        <v>4</v>
+      </c>
+      <c r="R46" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="S46" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="14">
+        <v>37</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="14">
         <v>35</v>
       </c>
-      <c r="G45" s="20">
-        <v>2</v>
-      </c>
-      <c r="R45" s="14" t="s">
+      <c r="G47" s="20">
+        <v>2</v>
+      </c>
+      <c r="R47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="S45" s="14" t="s">
+      <c r="S47" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="32">
+    <row r="48" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="32">
         <v>38</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="B48" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C48" s="33">
         <v>36</v>
       </c>
-      <c r="O46" s="54"/>
-      <c r="P46" s="54" t="s">
+      <c r="O48" s="54"/>
+      <c r="P48" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="Q46" s="54" t="s">
+      <c r="Q48" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="R46" s="33" t="s">
+      <c r="R48" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="S46" s="33" t="s">
+      <c r="S48" s="33" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="35">
-        <v>39</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="14">
-        <v>37</v>
-      </c>
-      <c r="O47" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="P47" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q47" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="R47" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="S47" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A48" s="35">
-        <v>40</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="14">
-        <v>38</v>
-      </c>
-      <c r="O48" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P48" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q48" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="R48" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S48" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C49" s="14">
-        <v>39</v>
-      </c>
-      <c r="O49" s="17">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="O49" s="17" t="s">
+        <v>150</v>
       </c>
       <c r="P49" s="17" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="Q49" s="17" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="R49" s="14" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="S49" s="14" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C50" s="14">
-        <v>40</v>
-      </c>
-      <c r="O50" s="17">
-        <v>50</v>
-      </c>
-      <c r="P50" s="17">
-        <v>100</v>
+        <v>38</v>
+      </c>
+      <c r="O50" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="P50" s="17" t="s">
+        <v>154</v>
       </c>
       <c r="Q50" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R50" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S50" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C51" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O51" s="17">
-        <v>60000</v>
+        <v>5</v>
       </c>
       <c r="P51" s="17" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="Q51" s="17" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="R51" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S51" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C52" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O52" s="17">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="P52" s="17">
+        <v>100</v>
       </c>
       <c r="Q52" s="17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="R52" s="14" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="S52" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C53" s="14">
+        <v>41</v>
+      </c>
+      <c r="O53" s="17">
+        <v>60000</v>
+      </c>
+      <c r="P53" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q53" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="R53" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S53" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="35">
+        <v>44</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="14">
+        <v>42</v>
+      </c>
+      <c r="O54" s="17">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="R54" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="S54" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" s="35">
+        <v>45</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="14">
         <v>43</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="Q55" t="s">
+        <v>174</v>
+      </c>
+      <c r="R55" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="36">
+        <v>46</v>
+      </c>
+      <c r="B56" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="37">
+        <v>44</v>
+      </c>
+      <c r="G56" s="37">
+        <v>5</v>
+      </c>
+      <c r="Q56"/>
+      <c r="R56" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="S56" s="37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>47</v>
+      </c>
+      <c r="B57" t="s">
         <v>175</v>
       </c>
-      <c r="R53" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="36">
-        <v>46</v>
-      </c>
-      <c r="B54" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="37">
-        <v>44</v>
-      </c>
-      <c r="G54" s="37">
-        <v>5</v>
-      </c>
-      <c r="Q54"/>
-      <c r="R54" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="S54" s="37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>47</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="C57">
+        <v>45</v>
+      </c>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57">
+        <v>-999</v>
+      </c>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57" t="s">
         <v>176</v>
-      </c>
-      <c r="C55">
-        <v>45</v>
-      </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55">
-        <v>-999</v>
-      </c>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-      <c r="R55" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C417E4-DA20-4C63-A6D1-57048F566C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C1FFA3-3BB9-4C95-BCFE-E7FA7681471A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I_1" sheetId="1" r:id="rId1"/>
@@ -1579,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="2">
-        <v>-997</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="s">
         <v>34</v>
@@ -6064,7 +6064,7 @@
         <v>35</v>
       </c>
       <c r="G38">
-        <v>-998</v>
+        <v>2</v>
       </c>
       <c r="R38" t="s">
         <v>86</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="H8" s="40"/>
       <c r="I8" s="40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="40"/>
       <c r="K8" s="40"/>

--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C1FFA3-3BB9-4C95-BCFE-E7FA7681471A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC06370-BAE3-4DD2-B796-D95C9D0ECD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I_1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="179">
   <si>
     <t>If the [extreme event] happen, how likely are you to go out fishing?</t>
   </si>
@@ -632,18 +632,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -671,13 +665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,76 +731,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -832,44 +775,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -883,12 +796,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1266,153 +1218,153 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="26">
-        <v>2</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="27">
-        <v>2</v>
-      </c>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="23">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="24">
         <v>4</v>
       </c>
-      <c r="J3" s="47">
-        <v>1</v>
-      </c>
-      <c r="K3" s="45">
-        <v>1</v>
-      </c>
-      <c r="L3" s="45">
-        <v>1</v>
-      </c>
-      <c r="M3" s="44">
+      <c r="J3" s="25">
+        <v>1</v>
+      </c>
+      <c r="K3" s="24">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24">
+        <v>1</v>
+      </c>
+      <c r="M3" s="25">
         <v>5</v>
       </c>
-      <c r="N3" s="43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
-        <v>2</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="23">
-        <v>2</v>
-      </c>
-      <c r="D4" s="23" t="s">
+      <c r="N3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26">
+        <v>2</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="27">
+        <v>2</v>
+      </c>
+      <c r="D4" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="43">
-        <v>1</v>
-      </c>
-      <c r="R4" s="23" t="s">
+      <c r="H4" s="25">
+        <v>1</v>
+      </c>
+      <c r="R4" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="23" t="s">
+      <c r="S4" s="27" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
-        <v>2</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="27">
-        <v>2</v>
-      </c>
-      <c r="D5" s="27" t="s">
+    <row r="5" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="23">
+        <v>2</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="24">
         <v>5</v>
       </c>
-      <c r="J5" s="48"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="45"/>
+      <c r="J5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
-        <v>3</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="27">
-        <v>3</v>
-      </c>
-      <c r="D6" s="33" t="s">
+      <c r="A6" s="22">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="23">
+        <v>3</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="45">
-        <v>2</v>
-      </c>
-      <c r="J6" s="47">
-        <v>2</v>
-      </c>
-      <c r="K6" s="45">
-        <v>2</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="H6" s="28"/>
+      <c r="I6" s="24">
+        <v>2</v>
+      </c>
+      <c r="J6" s="25">
+        <v>2</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="28">
         <v>-998</v>
       </c>
-      <c r="M6" s="43">
-        <v>2</v>
-      </c>
-      <c r="N6" s="45">
+      <c r="M6" s="25">
+        <v>2</v>
+      </c>
+      <c r="N6" s="24">
         <v>-998</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
-        <v>3</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="23">
-        <v>3</v>
-      </c>
-      <c r="D7" s="23" t="s">
+    <row r="7" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26">
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="27">
+        <v>3</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="43">
-        <v>1</v>
-      </c>
-      <c r="N7" s="43"/>
-    </row>
-    <row r="8" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
-        <v>3</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="27">
-        <v>3</v>
-      </c>
-      <c r="D8" s="27" t="s">
+      <c r="H7" s="25">
+        <v>1</v>
+      </c>
+      <c r="N7" s="25"/>
+    </row>
+    <row r="8" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="23">
+        <v>3</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="H8" s="45">
+      <c r="H8" s="24">
         <v>5</v>
       </c>
-      <c r="J8" s="48"/>
-      <c r="M8" s="45"/>
-      <c r="R8" s="27" t="s">
+      <c r="J8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="R8" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="S8" s="27" t="s">
+      <c r="S8" s="23" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1426,25 +1378,25 @@
       <c r="C9">
         <v>4</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="30">
         <v>-997</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="30">
         <v>-997</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="28">
         <v>-998</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="30">
         <v>-997</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="28">
         <v>-998</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="30">
         <v>-997</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="28">
         <v>-998</v>
       </c>
       <c r="R9" t="s">
@@ -1464,25 +1416,25 @@
       <c r="C10">
         <v>5</v>
       </c>
-      <c r="H10" s="6">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6">
-        <v>2</v>
-      </c>
-      <c r="J10" s="6">
-        <v>3</v>
-      </c>
-      <c r="K10" s="6">
-        <v>2</v>
-      </c>
-      <c r="L10" s="6">
-        <v>3</v>
-      </c>
-      <c r="M10" s="6">
-        <v>3</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="H10" s="28">
+        <v>3</v>
+      </c>
+      <c r="I10" s="28">
+        <v>2</v>
+      </c>
+      <c r="J10" s="28">
+        <v>3</v>
+      </c>
+      <c r="K10" s="28">
+        <v>2</v>
+      </c>
+      <c r="L10" s="28">
+        <v>3</v>
+      </c>
+      <c r="M10" s="28">
+        <v>3</v>
+      </c>
+      <c r="N10" s="28">
         <v>3</v>
       </c>
       <c r="R10" t="s">
@@ -1502,25 +1454,25 @@
       <c r="C11">
         <v>6</v>
       </c>
-      <c r="H11" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I11" s="6">
-        <v>3</v>
-      </c>
-      <c r="J11" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K11" s="6">
-        <v>3</v>
-      </c>
-      <c r="L11" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M11" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="H11" s="28">
+        <v>-999</v>
+      </c>
+      <c r="I11" s="28">
+        <v>3</v>
+      </c>
+      <c r="J11" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K11" s="28">
+        <v>3</v>
+      </c>
+      <c r="L11" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M11" s="28">
+        <v>-999</v>
+      </c>
+      <c r="N11" s="28">
         <v>-999</v>
       </c>
       <c r="R11" t="s">
@@ -1540,25 +1492,25 @@
       <c r="C12">
         <v>7</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="28">
         <v>4</v>
       </c>
-      <c r="I12" s="6">
-        <v>-999</v>
-      </c>
-      <c r="J12" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K12" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L12" s="7">
-        <v>-999</v>
-      </c>
-      <c r="M12" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N12" s="6">
+      <c r="I12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="J12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="L12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="N12" s="28">
         <v>-999</v>
       </c>
       <c r="R12" t="s">
@@ -1578,7 +1530,7 @@
       <c r="C13">
         <v>8</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13">
         <v>1.5</v>
       </c>
       <c r="R13" t="s">
@@ -1598,26 +1550,26 @@
       <c r="C14">
         <v>9</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6">
+      <c r="H14" s="28"/>
+      <c r="I14" s="28">
         <v>0</v>
       </c>
-      <c r="J14" s="6">
-        <v>2</v>
-      </c>
-      <c r="K14" s="6">
+      <c r="J14" s="28">
+        <v>2</v>
+      </c>
+      <c r="K14" s="28">
         <v>0</v>
       </c>
-      <c r="L14" s="6">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6">
-        <v>1</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="L14" s="28">
+        <v>1</v>
+      </c>
+      <c r="M14" s="28">
+        <v>1</v>
+      </c>
+      <c r="N14" s="28">
         <v>2</v>
       </c>
       <c r="R14" t="s">
@@ -1637,10 +1589,10 @@
       <c r="C15">
         <v>9</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="28">
         <v>1</v>
       </c>
     </row>
@@ -1654,25 +1606,25 @@
       <c r="C16">
         <v>10</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="28">
         <v>0</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="28">
         <v>0</v>
       </c>
-      <c r="J16" s="6">
-        <v>2</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="J16" s="28">
+        <v>2</v>
+      </c>
+      <c r="K16" s="28">
         <v>0</v>
       </c>
-      <c r="L16" s="9">
-        <v>2</v>
-      </c>
-      <c r="M16" s="6">
-        <v>1</v>
-      </c>
-      <c r="N16" s="6">
+      <c r="L16" s="28">
+        <v>2</v>
+      </c>
+      <c r="M16" s="28">
+        <v>1</v>
+      </c>
+      <c r="N16" s="28">
         <v>2</v>
       </c>
       <c r="R16" t="s">
@@ -1744,25 +1696,25 @@
       <c r="C19">
         <v>13</v>
       </c>
-      <c r="H19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="J19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M19" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N19" s="6">
+      <c r="H19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="I19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="J19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="L19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M19" s="28">
+        <v>-999</v>
+      </c>
+      <c r="N19" s="28">
         <v>-999</v>
       </c>
       <c r="R19" t="s">
@@ -1802,25 +1754,25 @@
       <c r="C21">
         <v>15</v>
       </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2">
-        <v>2</v>
-      </c>
-      <c r="L21" s="2">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2">
-        <v>1</v>
-      </c>
-      <c r="N21" s="2">
+      <c r="H21" s="31">
+        <v>1</v>
+      </c>
+      <c r="I21" s="31">
+        <v>2</v>
+      </c>
+      <c r="J21" s="31">
+        <v>1</v>
+      </c>
+      <c r="K21" s="31">
+        <v>2</v>
+      </c>
+      <c r="L21" s="31">
+        <v>1</v>
+      </c>
+      <c r="M21" s="31">
+        <v>1</v>
+      </c>
+      <c r="N21" s="31">
         <v>1</v>
       </c>
       <c r="R21" t="s">
@@ -1840,7 +1792,7 @@
       <c r="C22">
         <v>16</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22">
         <v>0</v>
       </c>
       <c r="R22" t="s">
@@ -1866,7 +1818,7 @@
       <c r="R23" t="s">
         <v>11</v>
       </c>
-      <c r="S23" s="8" t="s">
+      <c r="S23" s="29" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1886,7 +1838,7 @@
       <c r="R24" t="s">
         <v>53</v>
       </c>
-      <c r="S24" s="8" t="s">
+      <c r="S24" s="29" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1906,7 +1858,7 @@
       <c r="R25" t="s">
         <v>54</v>
       </c>
-      <c r="S25" s="8" t="s">
+      <c r="S25" s="29" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1926,7 +1878,7 @@
       <c r="R26" t="s">
         <v>56</v>
       </c>
-      <c r="S26" s="8" t="s">
+      <c r="S26" s="29" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1946,7 +1898,7 @@
       <c r="R27" t="s">
         <v>57</v>
       </c>
-      <c r="S27" s="8" t="s">
+      <c r="S27" s="29" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1966,7 +1918,7 @@
       <c r="R28" t="s">
         <v>58</v>
       </c>
-      <c r="S28" s="8" t="s">
+      <c r="S28" s="29" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1986,7 +1938,7 @@
       <c r="R29" t="s">
         <v>59</v>
       </c>
-      <c r="S29" s="8" t="s">
+      <c r="S29" s="29" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2000,7 +1952,7 @@
       <c r="C30">
         <v>22</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30">
         <v>4</v>
       </c>
       <c r="R30" t="s">
@@ -2040,7 +1992,7 @@
       <c r="C32">
         <v>24</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32">
         <v>4</v>
       </c>
       <c r="R32" t="s">
@@ -2080,7 +2032,7 @@
       <c r="C34">
         <v>26</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="31">
         <v>2</v>
       </c>
       <c r="R34" t="s">
@@ -2120,7 +2072,7 @@
       <c r="C36">
         <v>28</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36">
         <v>3</v>
       </c>
       <c r="R36" t="s">
@@ -2338,7 +2290,7 @@
       <c r="R46" t="s">
         <v>15</v>
       </c>
-      <c r="S46" s="8" t="s">
+      <c r="S46" s="29" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2364,7 +2316,7 @@
       <c r="R47" t="s">
         <v>16</v>
       </c>
-      <c r="S47" s="8" t="s">
+      <c r="S47" s="29" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2390,7 +2342,7 @@
       <c r="R48" t="s">
         <v>17</v>
       </c>
-      <c r="S48" s="8" t="s">
+      <c r="S48" s="29" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2416,7 +2368,7 @@
       <c r="R49" t="s">
         <v>18</v>
       </c>
-      <c r="S49" s="8" t="s">
+      <c r="S49" s="29" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2436,7 +2388,7 @@
       <c r="R50" t="s">
         <v>98</v>
       </c>
-      <c r="S50" s="8" t="s">
+      <c r="S50" s="29" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2473,7 +2425,7 @@
       <c r="R52" t="s">
         <v>100</v>
       </c>
-      <c r="S52" s="8" t="s">
+      <c r="S52" s="29" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2611,14 +2563,14 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>-999</v>
+      <c r="H3" s="31">
+        <v>2</v>
       </c>
       <c r="I3">
         <v>3</v>
       </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="J3" s="31">
+        <v>2</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -2649,25 +2601,25 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>-999</v>
-      </c>
-      <c r="I4" s="6">
-        <v>2</v>
-      </c>
-      <c r="J4" s="49">
+      <c r="H4" s="31">
+        <v>3</v>
+      </c>
+      <c r="I4" s="28">
+        <v>2</v>
+      </c>
+      <c r="J4" s="30">
         <v>-998</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="28">
         <v>-998</v>
       </c>
-      <c r="L4" s="6">
-        <v>3</v>
-      </c>
-      <c r="M4" s="6">
-        <v>2</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="L4" s="28">
+        <v>3</v>
+      </c>
+      <c r="M4" s="28">
+        <v>2</v>
+      </c>
+      <c r="N4" s="28">
         <v>1</v>
       </c>
       <c r="R4" t="s">
@@ -2687,25 +2639,25 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="H5">
-        <v>-999</v>
-      </c>
-      <c r="I5" s="6">
+      <c r="H5" s="31">
+        <v>1</v>
+      </c>
+      <c r="I5" s="28">
         <v>4</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="30">
         <v>-998</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="28">
         <v>-998</v>
       </c>
-      <c r="L5" s="6">
-        <v>1</v>
-      </c>
-      <c r="M5" s="6">
-        <v>1</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="L5" s="28">
+        <v>1</v>
+      </c>
+      <c r="M5" s="28">
+        <v>1</v>
+      </c>
+      <c r="N5" s="28">
         <v>-998</v>
       </c>
       <c r="R5" t="s">
@@ -2725,25 +2677,25 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="10" t="s">
         <v>169</v>
       </c>
       <c r="H6">
-        <v>-999</v>
-      </c>
-      <c r="J6" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K6" s="9">
-        <v>2</v>
-      </c>
-      <c r="L6" s="6">
+        <v>3</v>
+      </c>
+      <c r="J6" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K6" s="28">
+        <v>2</v>
+      </c>
+      <c r="L6" s="28">
         <v>-998</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="28">
         <v>-998</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="28">
         <v>-998</v>
       </c>
     </row>
@@ -2760,14 +2712,14 @@
       <c r="F7" t="s">
         <v>162</v>
       </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="I7" s="28">
+        <v>1</v>
+      </c>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -2805,22 +2757,22 @@
       <c r="H9">
         <v>-999</v>
       </c>
-      <c r="I9" s="6">
-        <v>3</v>
-      </c>
-      <c r="J9" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K9" s="6">
+      <c r="I9" s="28">
+        <v>3</v>
+      </c>
+      <c r="J9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K9" s="28">
         <v>4</v>
       </c>
-      <c r="L9" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M9" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N9" s="6">
+      <c r="L9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="N9" s="28">
         <v>-999</v>
       </c>
       <c r="R9" t="s">
@@ -2840,25 +2792,25 @@
       <c r="C10">
         <v>7</v>
       </c>
-      <c r="H10" s="49">
-        <v>3</v>
-      </c>
-      <c r="I10" s="6">
-        <v>3</v>
-      </c>
-      <c r="J10" s="6">
+      <c r="H10" s="28">
+        <v>3</v>
+      </c>
+      <c r="I10" s="28">
+        <v>3</v>
+      </c>
+      <c r="J10" s="28">
         <v>-998</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="28">
         <v>-998</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="28">
         <v>-998</v>
       </c>
-      <c r="M10" s="6">
-        <v>3</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="M10" s="28">
+        <v>3</v>
+      </c>
+      <c r="N10" s="28">
         <v>3</v>
       </c>
       <c r="R10" t="s">
@@ -2898,25 +2850,25 @@
       <c r="C12">
         <v>9</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="28">
         <v>0</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="28">
         <v>0</v>
       </c>
-      <c r="J12" s="9">
-        <v>2</v>
-      </c>
-      <c r="K12" s="9">
+      <c r="J12" s="28">
+        <v>2</v>
+      </c>
+      <c r="K12" s="28">
         <v>0</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="28">
         <v>0</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="28">
         <v>0</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="28">
         <v>2</v>
       </c>
       <c r="R12" t="s">
@@ -2936,26 +2888,26 @@
       <c r="C13">
         <v>10</v>
       </c>
-      <c r="H13" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I13" s="6">
-        <v>1</v>
-      </c>
-      <c r="J13" s="6">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6">
+      <c r="H13" s="41">
         <v>0</v>
       </c>
-      <c r="L13" s="6">
-        <v>1</v>
-      </c>
-      <c r="M13" s="6">
-        <v>1</v>
-      </c>
-      <c r="N13" s="9">
-        <v>2</v>
+      <c r="I13" s="28">
+        <v>1</v>
+      </c>
+      <c r="J13" s="28">
+        <v>1</v>
+      </c>
+      <c r="K13" s="28">
+        <v>0</v>
+      </c>
+      <c r="L13" s="28">
+        <v>1</v>
+      </c>
+      <c r="M13" s="28">
+        <v>1</v>
+      </c>
+      <c r="N13" s="30">
+        <v>1.5</v>
       </c>
       <c r="R13" t="s">
         <v>38</v>
@@ -3026,25 +2978,25 @@
       <c r="C16">
         <v>13</v>
       </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="H16" s="28">
+        <v>1</v>
+      </c>
+      <c r="I16" s="28">
+        <v>1</v>
+      </c>
+      <c r="J16" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K16" s="28">
         <v>0</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="28">
         <v>0</v>
       </c>
-      <c r="M16" s="6">
-        <v>2</v>
-      </c>
-      <c r="N16" s="6">
+      <c r="M16" s="28">
+        <v>2</v>
+      </c>
+      <c r="N16" s="28">
         <v>2</v>
       </c>
       <c r="R16" t="s">
@@ -3084,25 +3036,25 @@
       <c r="C18">
         <v>15</v>
       </c>
-      <c r="H18" s="6">
-        <v>2</v>
-      </c>
-      <c r="I18" s="6">
-        <v>2</v>
-      </c>
-      <c r="J18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="H18" s="28">
+        <v>2</v>
+      </c>
+      <c r="I18" s="28">
+        <v>2</v>
+      </c>
+      <c r="J18" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K18" s="28">
         <v>4</v>
       </c>
-      <c r="L18" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M18" s="6">
-        <v>1</v>
-      </c>
-      <c r="N18" s="6">
+      <c r="L18" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M18" s="28">
+        <v>1</v>
+      </c>
+      <c r="N18" s="28">
         <v>1</v>
       </c>
       <c r="R18" t="s">
@@ -3162,7 +3114,7 @@
       <c r="C21">
         <v>18</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21">
         <v>999</v>
       </c>
       <c r="R21" t="s">
@@ -3182,7 +3134,7 @@
       <c r="C22">
         <v>19</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22">
         <v>1</v>
       </c>
       <c r="R22" t="s">
@@ -3302,7 +3254,7 @@
       <c r="C28">
         <v>23</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28">
         <v>1</v>
       </c>
       <c r="R28" t="s">
@@ -3542,7 +3494,7 @@
       <c r="C40">
         <v>35</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="31">
         <v>2</v>
       </c>
       <c r="R40" t="s">
@@ -3562,10 +3514,10 @@
       <c r="C41">
         <v>36</v>
       </c>
-      <c r="O41" s="10">
+      <c r="O41" s="32">
         <v>50</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="28">
         <v>100</v>
       </c>
       <c r="Q41" t="s">
@@ -3700,13 +3652,13 @@
       <c r="C47">
         <v>42</v>
       </c>
-      <c r="O47" s="10">
-        <v>3</v>
-      </c>
-      <c r="P47" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="6" t="s">
+      <c r="O47" s="32">
+        <v>3</v>
+      </c>
+      <c r="P47" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="28" t="s">
         <v>128</v>
       </c>
       <c r="R47" t="s">
@@ -3898,39 +3850,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
-        <v>3</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="23">
-        <v>3</v>
-      </c>
-      <c r="F4" s="33" t="s">
+    <row r="4" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="27">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H4" s="23">
-        <v>-999</v>
-      </c>
-      <c r="I4" s="23">
-        <v>2</v>
-      </c>
-      <c r="J4" s="23">
-        <v>-999</v>
-      </c>
-      <c r="K4" s="24">
-        <v>3</v>
-      </c>
-      <c r="L4" s="23">
-        <v>3</v>
-      </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
+      <c r="H4" s="27">
+        <v>-999</v>
+      </c>
+      <c r="I4" s="27">
+        <v>2</v>
+      </c>
+      <c r="J4" s="27">
+        <v>-999</v>
+      </c>
+      <c r="K4" s="27">
+        <v>3</v>
+      </c>
+      <c r="L4" s="27">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="33">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -3945,11 +3895,9 @@
       <c r="K5">
         <v>2</v>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="33">
         <v>3</v>
       </c>
       <c r="B6" t="s">
@@ -3964,36 +3912,36 @@
       <c r="K6">
         <v>2</v>
       </c>
-      <c r="M6" s="2">
-        <v>999</v>
-      </c>
-      <c r="N6" s="2">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
-        <v>3</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="27">
-        <v>3</v>
-      </c>
-      <c r="F7" s="27" t="s">
+      <c r="M6" s="31">
+        <v>4</v>
+      </c>
+      <c r="N6" s="31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="23">
+        <v>3</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="M7" s="28">
-        <v>999</v>
-      </c>
-      <c r="N7" s="28">
-        <v>999</v>
-      </c>
-      <c r="R7" s="27" t="s">
+      <c r="M7" s="35">
+        <v>4</v>
+      </c>
+      <c r="N7" s="35">
+        <v>4</v>
+      </c>
+      <c r="R7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="S7" s="27" t="s">
+      <c r="S7" s="23" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4121,25 +4069,25 @@
       <c r="C11">
         <v>7</v>
       </c>
-      <c r="H11" s="2">
-        <v>-999</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2">
-        <v>-999</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
+      <c r="H11">
+        <v>-999</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>-999</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
@@ -4220,7 +4168,7 @@
       <c r="H14">
         <v>-999</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="42">
         <v>0</v>
       </c>
       <c r="J14">
@@ -4232,11 +4180,11 @@
       <c r="L14">
         <v>0</v>
       </c>
-      <c r="M14" s="2">
-        <v>999</v>
-      </c>
-      <c r="N14" s="2">
-        <v>999</v>
+      <c r="M14" s="31">
+        <v>2</v>
+      </c>
+      <c r="N14" s="31">
+        <v>2</v>
       </c>
       <c r="R14" t="s">
         <v>38</v>
@@ -4403,7 +4351,7 @@
       <c r="C20">
         <v>16</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20">
         <v>999</v>
       </c>
       <c r="R20" t="s">
@@ -4429,7 +4377,7 @@
       <c r="R21" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S21" s="34" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4449,7 +4397,7 @@
       <c r="R22" t="s">
         <v>53</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S22" s="34" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4469,7 +4417,7 @@
       <c r="R23" t="s">
         <v>54</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="S23" s="34" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4489,7 +4437,7 @@
       <c r="R24" t="s">
         <v>56</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="S24" s="34" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4509,7 +4457,7 @@
       <c r="R25" t="s">
         <v>57</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="S25" s="34" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4529,7 +4477,7 @@
       <c r="R26" t="s">
         <v>58</v>
       </c>
-      <c r="S26" s="1" t="s">
+      <c r="S26" s="34" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4549,7 +4497,7 @@
       <c r="R27" t="s">
         <v>59</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="S27" s="34" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4907,7 +4855,7 @@
       <c r="R44" t="s">
         <v>15</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="S44" s="34" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4933,7 +4881,7 @@
       <c r="R45" t="s">
         <v>16</v>
       </c>
-      <c r="S45" s="1" t="s">
+      <c r="S45" s="34" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4959,7 +4907,7 @@
       <c r="R46" t="s">
         <v>17</v>
       </c>
-      <c r="S46" s="1" t="s">
+      <c r="S46" s="34" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4985,7 +4933,7 @@
       <c r="R47" t="s">
         <v>18</v>
       </c>
-      <c r="S47" s="1" t="s">
+      <c r="S47" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5011,7 +4959,7 @@
       <c r="R48" t="s">
         <v>98</v>
       </c>
-      <c r="S48" s="1" t="s">
+      <c r="S48" s="34" t="s">
         <v>97</v>
       </c>
     </row>
@@ -5045,10 +4993,10 @@
       <c r="G50">
         <v>2</v>
       </c>
-      <c r="R50" s="1" t="s">
+      <c r="R50" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="S50" s="1" t="s">
+      <c r="S50" s="34" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5076,7 +5024,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD628265-A169-414F-BB6E-7496B95E445F}">
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="12.5546875" customWidth="1"/>
@@ -5171,25 +5119,25 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="28">
         <v>4</v>
       </c>
-      <c r="I3" s="6">
-        <v>2</v>
-      </c>
-      <c r="J3" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K3" s="6">
-        <v>1</v>
-      </c>
-      <c r="L3" s="6">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6">
-        <v>1</v>
-      </c>
-      <c r="N3" s="6">
+      <c r="I3" s="28">
+        <v>2</v>
+      </c>
+      <c r="J3" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K3" s="28">
+        <v>1</v>
+      </c>
+      <c r="L3" s="28">
+        <v>1</v>
+      </c>
+      <c r="M3" s="28">
+        <v>1</v>
+      </c>
+      <c r="N3" s="28">
         <v>1</v>
       </c>
       <c r="R3" t="s">
@@ -5199,1086 +5147,1106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="H4" s="6">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K4" s="6">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6">
-        <v>3</v>
-      </c>
-      <c r="M4" s="6">
-        <v>2</v>
-      </c>
-      <c r="N4" s="6">
-        <v>2</v>
-      </c>
-      <c r="R4" t="s">
+    <row r="4" spans="1:19" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="27">
+        <v>3</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="25">
+        <v>2</v>
+      </c>
+      <c r="I4" s="43">
+        <v>3</v>
+      </c>
+      <c r="J4" s="25">
+        <v>-999</v>
+      </c>
+      <c r="K4" s="25">
+        <v>1</v>
+      </c>
+      <c r="L4" s="25">
+        <v>3</v>
+      </c>
+      <c r="M4" s="25">
+        <v>2</v>
+      </c>
+      <c r="N4" s="25">
+        <v>2</v>
+      </c>
+      <c r="R4" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:19" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="23">
+        <v>3</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="23">
         <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6">
-        <v>-998</v>
-      </c>
-      <c r="I5" s="6">
-        <v>-998</v>
-      </c>
-      <c r="J5" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K5" s="49">
-        <v>5</v>
-      </c>
-      <c r="L5" s="6">
-        <v>-998</v>
-      </c>
-      <c r="M5" s="6">
-        <v>-998</v>
-      </c>
-      <c r="N5" s="6">
-        <v>-998</v>
-      </c>
-      <c r="R5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>108</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="H6" s="6">
-        <v>3</v>
-      </c>
-      <c r="I6" s="6">
-        <v>2</v>
-      </c>
-      <c r="J6" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K6" s="6">
+        <v>4</v>
+      </c>
+      <c r="H6" s="28">
         <v>-998</v>
       </c>
-      <c r="L6" s="6">
+      <c r="I6" s="28">
         <v>-998</v>
       </c>
-      <c r="M6" s="6">
+      <c r="J6" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K6" s="30">
         <v>-998</v>
       </c>
-      <c r="N6" s="6">
+      <c r="L6" s="28">
         <v>-998</v>
       </c>
+      <c r="M6" s="28">
+        <v>-998</v>
+      </c>
+      <c r="N6" s="28">
+        <v>-998</v>
+      </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>108</v>
       </c>
       <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="H7" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I7" s="6">
-        <v>3</v>
-      </c>
-      <c r="J7" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K7" s="6">
-        <v>-999</v>
-      </c>
-      <c r="L7" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M7" s="6">
-        <v>-999</v>
-      </c>
-      <c r="N7" s="6">
-        <v>-999</v>
+        <v>5</v>
+      </c>
+      <c r="H7" s="28">
+        <v>3</v>
+      </c>
+      <c r="I7" s="28">
+        <v>2</v>
+      </c>
+      <c r="J7" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K7" s="28">
+        <v>-998</v>
+      </c>
+      <c r="L7" s="28">
+        <v>-998</v>
+      </c>
+      <c r="M7" s="28">
+        <v>-998</v>
+      </c>
+      <c r="N7" s="28">
+        <v>-998</v>
       </c>
       <c r="R7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>108</v>
       </c>
       <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="H8" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I8" s="6">
-        <v>-999</v>
-      </c>
-      <c r="J8" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K8" s="6">
-        <v>5</v>
-      </c>
-      <c r="L8" s="6">
-        <v>-999</v>
-      </c>
-      <c r="M8" s="6">
-        <v>5</v>
-      </c>
-      <c r="N8" s="6">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="H8" s="28">
+        <v>-999</v>
+      </c>
+      <c r="I8" s="28">
+        <v>3</v>
+      </c>
+      <c r="J8" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K8" s="28">
+        <v>-999</v>
+      </c>
+      <c r="L8" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M8" s="28">
+        <v>-999</v>
+      </c>
+      <c r="N8" s="28">
+        <v>-999</v>
       </c>
       <c r="R8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>108</v>
       </c>
       <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="H9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="I9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="J9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K9" s="28">
+        <v>5</v>
+      </c>
+      <c r="L9" s="28">
+        <v>-999</v>
+      </c>
+      <c r="M9" s="28">
+        <v>5</v>
+      </c>
+      <c r="N9" s="28">
+        <v>5</v>
       </c>
       <c r="R9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>108</v>
       </c>
       <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>1</v>
-      </c>
-      <c r="N10" s="6">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="G10" s="28">
+        <v>2</v>
       </c>
       <c r="R10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="H11" s="6">
+        <v>9</v>
+      </c>
+      <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="6">
-        <v>1</v>
-      </c>
-      <c r="J11" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K11" s="6">
+      <c r="I11" s="28">
         <v>0</v>
       </c>
-      <c r="L11" s="6">
+      <c r="J11" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K11" s="28">
         <v>0</v>
       </c>
-      <c r="M11" s="6">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="L11" s="28">
+        <v>0</v>
+      </c>
+      <c r="M11" s="28">
+        <v>1</v>
+      </c>
+      <c r="N11" s="28">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="O12" s="6">
-        <v>200</v>
-      </c>
-      <c r="P12" s="6">
-        <v>2500</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="H12" s="28">
+        <v>0</v>
+      </c>
+      <c r="I12" s="28">
+        <v>1</v>
+      </c>
+      <c r="J12" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K12" s="28">
+        <v>0</v>
+      </c>
+      <c r="L12" s="28">
+        <v>0</v>
+      </c>
+      <c r="M12" s="28">
+        <v>1</v>
+      </c>
+      <c r="N12" s="28">
+        <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S12" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="O13" s="6">
+        <v>11</v>
+      </c>
+      <c r="O13" s="28">
+        <v>200</v>
+      </c>
+      <c r="P13" s="28">
         <v>2500</v>
       </c>
-      <c r="P13" s="6">
-        <v>5000</v>
-      </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="28" t="s">
         <v>91</v>
       </c>
       <c r="R13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>108</v>
       </c>
       <c r="C14">
-        <v>13</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K14" s="6">
-        <v>2</v>
-      </c>
-      <c r="L14" s="6">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6">
-        <v>2</v>
-      </c>
-      <c r="N14" s="6">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="O14" s="28">
+        <v>2500</v>
+      </c>
+      <c r="P14" s="28">
+        <v>5000</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>91</v>
       </c>
       <c r="R14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>108</v>
       </c>
       <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="G15" s="6">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="H15" s="28">
+        <v>0</v>
+      </c>
+      <c r="I15" s="28">
+        <v>1</v>
+      </c>
+      <c r="J15" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K15" s="28">
+        <v>2</v>
+      </c>
+      <c r="L15" s="28">
+        <v>1</v>
+      </c>
+      <c r="M15" s="28">
+        <v>2</v>
+      </c>
+      <c r="N15" s="28">
+        <v>2</v>
       </c>
       <c r="R15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="H16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="I16" s="6">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6">
-        <v>-999</v>
-      </c>
-      <c r="K16" s="56">
-        <v>1</v>
-      </c>
-      <c r="L16" s="6">
-        <v>1</v>
-      </c>
-      <c r="M16" s="6">
-        <v>4</v>
-      </c>
-      <c r="N16" s="56">
+        <v>14</v>
+      </c>
+      <c r="G16" s="28">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>110</v>
       </c>
       <c r="C17">
-        <v>16</v>
-      </c>
-      <c r="G17" s="6">
+        <v>15</v>
+      </c>
+      <c r="H17" s="28">
+        <v>-999</v>
+      </c>
+      <c r="I17" s="28">
+        <v>1</v>
+      </c>
+      <c r="J17" s="28">
+        <v>-999</v>
+      </c>
+      <c r="K17" s="28">
+        <v>1</v>
+      </c>
+      <c r="L17" s="28">
+        <v>1</v>
+      </c>
+      <c r="M17" s="28">
+        <v>4</v>
+      </c>
+      <c r="N17" s="28">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="S17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>110</v>
       </c>
       <c r="C18">
-        <v>17</v>
-      </c>
-      <c r="G18" s="6">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="G18" s="28">
+        <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>110</v>
       </c>
       <c r="C19">
-        <v>18</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G19" s="28">
+        <v>2</v>
       </c>
       <c r="R19" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="S19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>110</v>
       </c>
       <c r="C20">
-        <v>19</v>
-      </c>
-      <c r="G20" s="9">
-        <v>999</v>
+        <v>18</v>
+      </c>
+      <c r="G20" s="28">
+        <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>110</v>
       </c>
       <c r="C21">
-        <v>20</v>
-      </c>
-      <c r="G21" s="6">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="G21" s="28">
+        <v>999</v>
       </c>
       <c r="R21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="6">
-        <v>3</v>
+        <v>110</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="G22" s="28">
+        <v>2</v>
       </c>
       <c r="R22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="6">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="G23" s="28">
+        <v>3</v>
       </c>
       <c r="R23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="6">
+        <v>66</v>
+      </c>
+      <c r="G24" s="28">
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>111</v>
       </c>
-      <c r="C25">
-        <v>22</v>
-      </c>
-      <c r="G25" s="6">
-        <v>2</v>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="28">
+        <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="S25" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26">
-        <v>23</v>
-      </c>
-      <c r="G26" s="6">
-        <v>-999</v>
+        <v>22</v>
+      </c>
+      <c r="G26" s="28">
+        <v>2</v>
       </c>
       <c r="R26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S26" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>112</v>
       </c>
       <c r="C27">
-        <v>24</v>
-      </c>
-      <c r="G27" s="6">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="G27" s="28">
+        <v>-999</v>
       </c>
       <c r="R27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>112</v>
       </c>
       <c r="C28">
-        <v>25</v>
-      </c>
-      <c r="G28" s="6">
-        <v>-999</v>
+        <v>24</v>
+      </c>
+      <c r="G28" s="28">
+        <v>2</v>
       </c>
       <c r="R28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>112</v>
       </c>
       <c r="C29">
-        <v>26</v>
-      </c>
-      <c r="G29" s="6">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="G29" s="28">
+        <v>-999</v>
       </c>
       <c r="R29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S29" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30">
-        <v>27</v>
-      </c>
-      <c r="G30">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="G30" s="28">
+        <v>2</v>
       </c>
       <c r="R30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="S30" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>113</v>
       </c>
       <c r="C31">
-        <v>28</v>
-      </c>
-      <c r="G31" s="6">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
       </c>
       <c r="R31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S31" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>113</v>
       </c>
       <c r="C32">
-        <v>29</v>
-      </c>
-      <c r="G32">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="G32" s="28">
+        <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>113</v>
       </c>
       <c r="C33">
-        <v>30</v>
-      </c>
-      <c r="G33" s="6">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
       </c>
       <c r="R33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>113</v>
       </c>
       <c r="C34">
-        <v>31</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="G34" s="28">
+        <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="S34" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C35">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R35" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="S35" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>114</v>
       </c>
       <c r="C36">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>114</v>
       </c>
       <c r="C37">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="R37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S37" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>114</v>
       </c>
       <c r="C38">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C39">
-        <v>36</v>
-      </c>
-      <c r="O39" s="6">
-        <v>10</v>
-      </c>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6" t="s">
-        <v>157</v>
+        <v>35</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
       </c>
       <c r="R39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S39" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>36</v>
+      </c>
+      <c r="O40" s="28">
+        <v>10</v>
+      </c>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="R40" t="s">
+        <v>87</v>
+      </c>
+      <c r="S40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40">
-        <v>37</v>
-      </c>
-      <c r="O40" s="11"/>
-      <c r="Q40" t="s">
-        <v>174</v>
-      </c>
-      <c r="R40" t="s">
-        <v>88</v>
-      </c>
-      <c r="S40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41">
-        <v>38</v>
-      </c>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6">
-        <v>5000</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>92</v>
+        <v>37</v>
+      </c>
+      <c r="O41" s="36"/>
+      <c r="Q41" t="s">
+        <v>174</v>
       </c>
       <c r="R41" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="S41" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42">
-        <v>39</v>
-      </c>
-      <c r="O42" s="6">
+        <v>38</v>
+      </c>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28">
         <v>5000</v>
       </c>
-      <c r="P42" s="6">
-        <v>20000</v>
-      </c>
-      <c r="Q42" s="6" t="s">
+      <c r="Q42" s="28" t="s">
         <v>92</v>
       </c>
       <c r="R42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43">
-        <v>40</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>174</v>
+        <v>39</v>
+      </c>
+      <c r="O43" s="28">
+        <v>5000</v>
+      </c>
+      <c r="P43" s="28">
+        <v>20000</v>
+      </c>
+      <c r="Q43" s="28" t="s">
+        <v>92</v>
       </c>
       <c r="R43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44" t="s">
         <v>174</v>
       </c>
       <c r="R44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q45" t="s">
         <v>174</v>
       </c>
       <c r="R45" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="S45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q46" t="s">
         <v>174</v>
       </c>
       <c r="R46" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="S46" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47">
-        <v>44</v>
-      </c>
-      <c r="G47" s="55">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>174</v>
       </c>
       <c r="R47" t="s">
-        <v>100</v>
-      </c>
-      <c r="S47" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48">
+        <v>44</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="R48" t="s">
+        <v>100</v>
+      </c>
+      <c r="S48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>175</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>45</v>
       </c>
-      <c r="G48">
-        <v>-999</v>
-      </c>
-      <c r="R48" t="s">
+      <c r="G49">
+        <v>-999</v>
+      </c>
+      <c r="R49" t="s">
         <v>176</v>
       </c>
     </row>
@@ -6365,44 +6333,44 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
-        <v>2</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="23">
-        <v>2</v>
-      </c>
-      <c r="F3" s="33" t="s">
+    <row r="3" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="27">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29">
-        <v>1</v>
-      </c>
-      <c r="K3" s="29" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="37">
+        <v>1</v>
+      </c>
+      <c r="K3" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -6419,7 +6387,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="33">
         <v>2</v>
       </c>
       <c r="B5" t="s">
@@ -6436,7 +6404,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="33">
         <v>2</v>
       </c>
       <c r="B6" t="s">
@@ -6453,7 +6421,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="33">
         <v>2</v>
       </c>
       <c r="B7" t="s">
@@ -6469,61 +6437,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
-        <v>2</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="27">
-        <v>2</v>
-      </c>
-      <c r="F8" s="27" t="s">
+    <row r="8" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22">
+        <v>2</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="23">
+        <v>2</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="I8" s="27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22">
-        <v>3</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="23">
-        <v>3</v>
-      </c>
-      <c r="F9" s="33" t="s">
+      <c r="I8" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>3</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="27">
+        <v>3</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="37">
         <v>-997</v>
       </c>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29">
-        <v>2</v>
-      </c>
-      <c r="K9" s="29">
+      <c r="I9" s="37"/>
+      <c r="J9" s="37">
+        <v>2</v>
+      </c>
+      <c r="K9" s="37">
         <v>-998</v>
       </c>
-      <c r="L9" s="29">
-        <v>3</v>
-      </c>
-      <c r="M9" s="29" t="s">
+      <c r="L9" s="37">
+        <v>3</v>
+      </c>
+      <c r="M9" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="N9" s="29">
+      <c r="N9" s="37">
         <v>-998</v>
       </c>
-      <c r="R9" s="23" t="s">
+      <c r="R9" s="27" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="A10" s="33">
         <v>3</v>
       </c>
       <c r="B10" t="s">
@@ -6535,18 +6503,18 @@
       <c r="F10" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10">
+      <c r="H10" s="32"/>
+      <c r="I10" s="32">
         <v>4</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+      <c r="A11" s="33">
         <v>3</v>
       </c>
       <c r="B11" t="s">
@@ -6558,18 +6526,18 @@
       <c r="F11" t="s">
         <v>162</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10">
+      <c r="H11" s="32"/>
+      <c r="I11" s="32">
         <v>4</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="A12" s="33">
         <v>3</v>
       </c>
       <c r="B12" t="s">
@@ -6581,18 +6549,18 @@
       <c r="F12" t="s">
         <v>166</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10">
-        <v>2</v>
-      </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32">
+        <v>2</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="A13" s="33">
         <v>3</v>
       </c>
       <c r="B13" t="s">
@@ -6604,38 +6572,38 @@
       <c r="F13" t="s">
         <v>163</v>
       </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10">
-        <v>2</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
-        <v>3</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="27">
-        <v>3</v>
-      </c>
-      <c r="F14" s="27" t="s">
+      <c r="H13" s="32"/>
+      <c r="I13" s="32">
+        <v>2</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="22">
+        <v>3</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="23">
+        <v>3</v>
+      </c>
+      <c r="F14" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31">
-        <v>2</v>
-      </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38">
+        <v>2</v>
+      </c>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -6647,25 +6615,25 @@
       <c r="C15">
         <v>4</v>
       </c>
-      <c r="H15" s="10">
-        <v>1</v>
-      </c>
-      <c r="I15" s="10">
-        <v>2</v>
-      </c>
-      <c r="J15" s="10">
+      <c r="H15" s="32">
+        <v>1</v>
+      </c>
+      <c r="I15" s="32">
+        <v>2</v>
+      </c>
+      <c r="J15" s="32">
         <v>-998</v>
       </c>
-      <c r="K15" s="10">
-        <v>1</v>
-      </c>
-      <c r="L15" s="10">
-        <v>1</v>
-      </c>
-      <c r="M15" s="12">
+      <c r="K15" s="32">
+        <v>1</v>
+      </c>
+      <c r="L15" s="32">
+        <v>1</v>
+      </c>
+      <c r="M15" s="32">
         <v>999</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="32">
         <v>999</v>
       </c>
       <c r="R15" t="s">
@@ -6682,25 +6650,25 @@
       <c r="C16">
         <v>5</v>
       </c>
-      <c r="H16" s="10">
-        <v>3</v>
-      </c>
-      <c r="I16" s="10">
-        <v>2</v>
-      </c>
-      <c r="J16" s="10">
+      <c r="H16" s="32">
+        <v>3</v>
+      </c>
+      <c r="I16" s="32">
+        <v>2</v>
+      </c>
+      <c r="J16" s="32">
         <v>-998</v>
       </c>
-      <c r="K16" s="10">
-        <v>3</v>
-      </c>
-      <c r="L16" s="10">
-        <v>3</v>
-      </c>
-      <c r="M16" s="10">
-        <v>3</v>
-      </c>
-      <c r="N16" s="10">
+      <c r="K16" s="32">
+        <v>3</v>
+      </c>
+      <c r="L16" s="32">
+        <v>3</v>
+      </c>
+      <c r="M16" s="32">
+        <v>3</v>
+      </c>
+      <c r="N16" s="32">
         <v>3</v>
       </c>
       <c r="R16" t="s">
@@ -6717,25 +6685,25 @@
       <c r="C17">
         <v>6</v>
       </c>
-      <c r="H17" s="10">
-        <v>-999</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1</v>
-      </c>
-      <c r="J17" s="10">
-        <v>-999</v>
-      </c>
-      <c r="K17" s="10">
-        <v>-999</v>
-      </c>
-      <c r="L17" s="10">
-        <v>-999</v>
-      </c>
-      <c r="M17" s="10">
-        <v>-999</v>
-      </c>
-      <c r="N17" s="10">
+      <c r="H17" s="32">
+        <v>-999</v>
+      </c>
+      <c r="I17" s="32">
+        <v>1</v>
+      </c>
+      <c r="J17" s="32">
+        <v>-999</v>
+      </c>
+      <c r="K17" s="32">
+        <v>-999</v>
+      </c>
+      <c r="L17" s="32">
+        <v>-999</v>
+      </c>
+      <c r="M17" s="32">
+        <v>-999</v>
+      </c>
+      <c r="N17" s="32">
         <v>-999</v>
       </c>
       <c r="R17" t="s">
@@ -6752,25 +6720,25 @@
       <c r="C18">
         <v>7</v>
       </c>
-      <c r="H18" s="10">
-        <v>-999</v>
-      </c>
-      <c r="I18" s="12">
-        <v>3</v>
-      </c>
-      <c r="J18" s="10">
-        <v>-999</v>
-      </c>
-      <c r="K18" s="10">
-        <v>-999</v>
-      </c>
-      <c r="L18" s="10">
-        <v>-999</v>
-      </c>
-      <c r="M18" s="10">
-        <v>-999</v>
-      </c>
-      <c r="N18" s="10">
+      <c r="H18" s="32">
+        <v>-999</v>
+      </c>
+      <c r="I18" s="32">
+        <v>3</v>
+      </c>
+      <c r="J18" s="32">
+        <v>-999</v>
+      </c>
+      <c r="K18" s="32">
+        <v>-999</v>
+      </c>
+      <c r="L18" s="32">
+        <v>-999</v>
+      </c>
+      <c r="M18" s="32">
+        <v>-999</v>
+      </c>
+      <c r="N18" s="32">
         <v>-999</v>
       </c>
       <c r="R18" t="s">
@@ -6787,7 +6755,7 @@
       <c r="C19">
         <v>8</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="28">
         <v>5</v>
       </c>
       <c r="R19" t="s">
@@ -6804,25 +6772,25 @@
       <c r="C20">
         <v>9</v>
       </c>
-      <c r="H20" s="13">
-        <v>2</v>
-      </c>
-      <c r="I20" s="10">
+      <c r="H20" s="32">
+        <v>2</v>
+      </c>
+      <c r="I20" s="32">
         <v>0</v>
       </c>
-      <c r="J20" s="50">
-        <v>1</v>
-      </c>
-      <c r="K20" s="10">
+      <c r="J20" s="32">
+        <v>1</v>
+      </c>
+      <c r="K20" s="32">
         <v>0</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="32">
         <v>0</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="32">
         <v>0</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="32">
         <v>2</v>
       </c>
       <c r="R20" t="s">
@@ -6839,25 +6807,25 @@
       <c r="C21">
         <v>10</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="32">
         <v>0</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="32">
         <v>0</v>
       </c>
-      <c r="J21" s="10">
-        <v>1</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="J21" s="32">
+        <v>1</v>
+      </c>
+      <c r="K21" s="32">
         <v>0</v>
       </c>
-      <c r="L21" s="10">
-        <v>3</v>
-      </c>
-      <c r="M21" s="10">
+      <c r="L21" s="32">
+        <v>3</v>
+      </c>
+      <c r="M21" s="32">
         <v>0</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="32">
         <v>3</v>
       </c>
       <c r="R21" t="s">
@@ -6874,13 +6842,13 @@
       <c r="C22">
         <v>11</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="32">
         <v>10000</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="32">
         <v>50000</v>
       </c>
-      <c r="Q22" s="10" t="s">
+      <c r="Q22" s="32" t="s">
         <v>91</v>
       </c>
       <c r="R22" t="s">
@@ -6897,57 +6865,57 @@
       <c r="C23">
         <v>12</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="32">
         <v>50000</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="32">
         <v>1000000</v>
       </c>
-      <c r="Q23" s="10" t="s">
+      <c r="Q23" s="32" t="s">
         <v>91</v>
       </c>
       <c r="R23" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="22">
+    <row r="24" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="26">
         <v>13</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="23">
+      <c r="B24" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="27">
         <v>13</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H24" s="29">
-        <v>2</v>
-      </c>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
+      <c r="H24" s="37">
+        <v>2</v>
+      </c>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37">
         <v>-998</v>
       </c>
-      <c r="K24" s="29">
-        <v>1</v>
-      </c>
-      <c r="L24" s="29">
-        <v>2</v>
-      </c>
-      <c r="M24" s="29">
-        <v>1</v>
-      </c>
-      <c r="N24" s="29">
-        <v>1</v>
-      </c>
-      <c r="R24" s="23" t="s">
+      <c r="K24" s="37">
+        <v>1</v>
+      </c>
+      <c r="L24" s="37">
+        <v>2</v>
+      </c>
+      <c r="M24" s="37">
+        <v>1</v>
+      </c>
+      <c r="N24" s="37">
+        <v>1</v>
+      </c>
+      <c r="R24" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="25">
+      <c r="A25" s="33">
         <v>13</v>
       </c>
       <c r="B25" t="s">
@@ -6962,24 +6930,24 @@
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-    </row>
-    <row r="26" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26">
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+    </row>
+    <row r="26" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="22">
         <v>13</v>
       </c>
-      <c r="B26" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="27">
+      <c r="B26" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="23">
         <v>13</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="23">
         <v>2</v>
       </c>
     </row>
@@ -6993,7 +6961,7 @@
       <c r="C27">
         <v>14</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="28">
         <v>5</v>
       </c>
       <c r="R27" t="s">
@@ -7010,25 +6978,25 @@
       <c r="C28">
         <v>15</v>
       </c>
-      <c r="H28" s="10">
-        <v>2</v>
-      </c>
-      <c r="I28" s="10">
-        <v>2</v>
-      </c>
-      <c r="J28" s="10">
+      <c r="H28" s="32">
+        <v>2</v>
+      </c>
+      <c r="I28" s="32">
+        <v>2</v>
+      </c>
+      <c r="J28" s="32">
         <v>-998</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="32">
         <v>4</v>
       </c>
-      <c r="L28" s="10">
-        <v>2</v>
-      </c>
-      <c r="M28" s="10">
-        <v>3</v>
-      </c>
-      <c r="N28" s="10">
+      <c r="L28" s="32">
+        <v>2</v>
+      </c>
+      <c r="M28" s="32">
+        <v>3</v>
+      </c>
+      <c r="N28" s="32">
         <v>1</v>
       </c>
       <c r="R28" t="s">
@@ -7045,7 +7013,7 @@
       <c r="C29">
         <v>16</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="28">
         <v>1</v>
       </c>
       <c r="R29" t="s">
@@ -7062,7 +7030,7 @@
       <c r="C30">
         <v>17</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="28">
         <v>1</v>
       </c>
       <c r="R30" t="s">
@@ -7079,7 +7047,7 @@
       <c r="C31">
         <v>18</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="28">
         <v>2</v>
       </c>
       <c r="R31" t="s">
@@ -7096,7 +7064,7 @@
       <c r="C32">
         <v>19</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="28">
         <v>1</v>
       </c>
       <c r="R32" t="s">
@@ -7113,7 +7081,7 @@
       <c r="C33">
         <v>20</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="28">
         <v>4</v>
       </c>
       <c r="R33" t="s">
@@ -7130,7 +7098,7 @@
       <c r="C34" t="s">
         <v>65</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="28">
         <v>1</v>
       </c>
       <c r="R34" t="s">
@@ -7147,7 +7115,7 @@
       <c r="C35" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="28">
         <v>1</v>
       </c>
       <c r="R35" t="s">
@@ -7164,7 +7132,7 @@
       <c r="C36" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="28">
         <v>1</v>
       </c>
       <c r="R36" t="s">
@@ -7181,7 +7149,7 @@
       <c r="C37">
         <v>22</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="28">
         <v>2</v>
       </c>
       <c r="R37" t="s">
@@ -7198,7 +7166,7 @@
       <c r="C38">
         <v>23</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="28">
         <v>-999</v>
       </c>
       <c r="R38" t="s">
@@ -7215,7 +7183,7 @@
       <c r="C39">
         <v>24</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="28">
         <v>4</v>
       </c>
       <c r="R39" t="s">
@@ -7232,7 +7200,7 @@
       <c r="C40">
         <v>25</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="28">
         <v>-999</v>
       </c>
       <c r="R40" t="s">
@@ -7249,7 +7217,7 @@
       <c r="C41">
         <v>26</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="28">
         <v>4</v>
       </c>
       <c r="R41" t="s">
@@ -7283,7 +7251,7 @@
       <c r="C43">
         <v>28</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="28">
         <v>5</v>
       </c>
       <c r="R43" t="s">
@@ -7300,7 +7268,7 @@
       <c r="C44">
         <v>29</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44">
         <v>999</v>
       </c>
       <c r="R44" t="s">
@@ -7317,7 +7285,7 @@
       <c r="C45">
         <v>30</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="28">
         <v>3</v>
       </c>
       <c r="R45" t="s">
@@ -7419,13 +7387,13 @@
       <c r="C51">
         <v>36</v>
       </c>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="P51" s="11" t="s">
+      <c r="P51" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="Q51" s="11" t="s">
+      <c r="Q51" s="36" t="s">
         <v>138</v>
       </c>
       <c r="R51" t="s">
@@ -7442,7 +7410,7 @@
       <c r="C52">
         <v>37</v>
       </c>
-      <c r="O52" s="11"/>
+      <c r="O52" s="36"/>
       <c r="Q52" t="s">
         <v>174</v>
       </c>
@@ -7460,13 +7428,13 @@
       <c r="C53">
         <v>38</v>
       </c>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="P53" s="11" t="s">
+      <c r="P53" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="Q53" s="11" t="s">
+      <c r="Q53" s="36" t="s">
         <v>140</v>
       </c>
       <c r="R53" t="s">
@@ -7483,13 +7451,13 @@
       <c r="C54">
         <v>39</v>
       </c>
-      <c r="O54" s="11">
+      <c r="O54" s="36">
         <v>30</v>
       </c>
-      <c r="P54" s="11" t="s">
+      <c r="P54" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="Q54" s="11" t="s">
+      <c r="Q54" s="36" t="s">
         <v>142</v>
       </c>
       <c r="R54" t="s">
@@ -7506,13 +7474,13 @@
       <c r="C55">
         <v>40</v>
       </c>
-      <c r="O55" s="11">
+      <c r="O55" s="36">
         <v>20</v>
       </c>
-      <c r="P55" s="11" t="s">
+      <c r="P55" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="Q55" s="11" t="s">
+      <c r="Q55" s="36" t="s">
         <v>142</v>
       </c>
       <c r="R55" t="s">
@@ -7546,13 +7514,13 @@
       <c r="C57">
         <v>42</v>
       </c>
-      <c r="O57" s="11">
+      <c r="O57" s="36">
         <v>999</v>
       </c>
-      <c r="P57" s="11" t="s">
+      <c r="P57" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="Q57" s="11" t="s">
+      <c r="Q57" s="36" t="s">
         <v>143</v>
       </c>
       <c r="R57" t="s">
@@ -7620,1289 +7588,1289 @@
   <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16" width="8.88671875" style="14"/>
-    <col min="17" max="17" width="12.5546875" style="14" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="14"/>
+    <col min="1" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="12.5546875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32">
-        <v>2</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="33">
-        <v>2</v>
-      </c>
-      <c r="E3" s="33" t="s">
+    <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="11">
         <v>1.5</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="J3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="K3" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="11">
         <v>5</v>
       </c>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34" t="s">
+      <c r="M3" s="11"/>
+      <c r="N3" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="37" t="s">
+      <c r="R3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="37" t="s">
+      <c r="S3" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="35">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="14">
-        <v>2</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="1">
         <v>4</v>
       </c>
-      <c r="R4" s="37" t="s">
+      <c r="R4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="37" t="s">
+      <c r="S4" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36">
-        <v>2</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="37">
-        <v>2</v>
-      </c>
-      <c r="E5" s="37" t="s">
+    <row r="5" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="M5" s="57">
-        <v>1</v>
-      </c>
-      <c r="R5" s="37" t="s">
+      <c r="M5" s="14">
+        <v>1</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32">
-        <v>3</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="33">
-        <v>3</v>
-      </c>
-      <c r="E6" s="33" t="s">
+    <row r="6" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H6" s="39">
-        <v>3</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34" t="s">
+      <c r="H6" s="11">
+        <v>3</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="K6" s="34">
-        <v>1</v>
-      </c>
-      <c r="L6" s="34">
-        <v>3</v>
-      </c>
-      <c r="M6" s="34">
-        <v>3</v>
-      </c>
-      <c r="N6" s="34">
-        <v>2</v>
-      </c>
-      <c r="R6" s="33" t="s">
+      <c r="K6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="11">
+        <v>3</v>
+      </c>
+      <c r="M6" s="11">
+        <v>3</v>
+      </c>
+      <c r="N6" s="11">
+        <v>2</v>
+      </c>
+      <c r="R6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="S6" s="33" t="s">
+      <c r="S6" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="35">
-        <v>3</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="14">
-        <v>3</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="A7" s="12">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I7" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36">
-        <v>3</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="37">
-        <v>3</v>
-      </c>
-      <c r="E8" s="37" t="s">
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>3</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="14">
+        <v>3</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="B9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="15">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1</v>
-      </c>
-      <c r="J9" s="15">
-        <v>1</v>
-      </c>
-      <c r="K9" s="15">
-        <v>1</v>
-      </c>
-      <c r="L9" s="15">
-        <v>1</v>
-      </c>
-      <c r="M9" s="15">
-        <v>1</v>
-      </c>
-      <c r="N9" s="15">
-        <v>1</v>
-      </c>
-      <c r="R9" s="14" t="s">
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="S9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="14">
+      <c r="B10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="16">
-        <v>2</v>
-      </c>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="15">
-        <v>3</v>
-      </c>
-      <c r="K10" s="15">
-        <v>3</v>
-      </c>
-      <c r="L10" s="15">
-        <v>3</v>
-      </c>
-      <c r="M10" s="15">
-        <v>1</v>
-      </c>
-      <c r="N10" s="15">
-        <v>1</v>
-      </c>
-      <c r="R10" s="14" t="s">
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="S10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="2">
         <v>5</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="2">
         <v>5</v>
       </c>
-      <c r="J11" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K11" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L11" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M11" s="15">
-        <v>3</v>
-      </c>
-      <c r="N11" s="15">
-        <v>3</v>
-      </c>
-      <c r="R11" s="14" t="s">
+      <c r="J11" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K11" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L11" s="2">
+        <v>-999</v>
+      </c>
+      <c r="M11" s="2">
+        <v>3</v>
+      </c>
+      <c r="N11" s="2">
+        <v>3</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="1">
         <v>7</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="14">
+      <c r="B12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="2">
         <v>4</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J12" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K12" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L12" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M12" s="15">
-        <v>-999</v>
-      </c>
-      <c r="N12" s="15">
-        <v>-999</v>
-      </c>
-      <c r="R12" s="14" t="s">
+      <c r="J12" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K12" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L12" s="2">
+        <v>-999</v>
+      </c>
+      <c r="M12" s="2">
+        <v>-999</v>
+      </c>
+      <c r="N12" s="2">
+        <v>-999</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S12" s="14" t="s">
+      <c r="S12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="14">
+      <c r="B13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="G13" s="51">
-        <v>3</v>
-      </c>
-      <c r="H13" s="17"/>
-      <c r="R13" s="14" t="s">
+      <c r="G13" s="18">
+        <v>3</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="R13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S13" s="14" t="s">
+      <c r="S13" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="14">
+      <c r="B14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="21">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="H14" s="39">
         <v>0</v>
       </c>
-      <c r="J14" s="15">
-        <v>2</v>
-      </c>
-      <c r="K14" s="15">
+      <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="L14" s="15">
-        <v>1</v>
-      </c>
-      <c r="M14" s="15">
-        <v>1</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="J14" s="2">
+        <v>2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
         <v>2.5</v>
       </c>
-      <c r="R14" s="14" t="s">
+      <c r="R14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="21">
-        <v>3</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="H15" s="39">
         <v>0</v>
       </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="15">
+      <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="15">
+      <c r="J15" s="2">
+        <v>3</v>
+      </c>
+      <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="M15" s="15">
+      <c r="L15" s="2">
         <v>0</v>
       </c>
-      <c r="N15" s="15">
-        <v>3</v>
-      </c>
-      <c r="R15" s="14" t="s">
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>3</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="S15" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
+      <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O16" s="2">
         <v>10000</v>
       </c>
-      <c r="P16" s="15">
+      <c r="P16" s="2">
         <v>50000</v>
       </c>
-      <c r="Q16" s="15" t="s">
+      <c r="Q16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R16" s="14" t="s">
+      <c r="R16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="2">
         <v>100000</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="2">
         <v>500000</v>
       </c>
-      <c r="Q17" s="15" t="s">
+      <c r="Q17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R17" s="14" t="s">
+      <c r="R17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="H18" s="21">
-        <v>2</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="15">
-        <v>2</v>
-      </c>
-      <c r="K18" s="15">
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="2">
         <v>0</v>
       </c>
-      <c r="N18" s="15">
-        <v>2</v>
-      </c>
-      <c r="R18" s="14" t="s">
+      <c r="N18" s="2">
+        <v>2</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S18" s="14" t="s">
+      <c r="S18" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="1">
         <v>14</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="14">
+      <c r="B19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="18">
         <v>4</v>
       </c>
-      <c r="R19" s="14" t="s">
+      <c r="R19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S19" s="14" t="s">
+      <c r="S19" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="1">
         <v>15</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="2">
         <v>3.5</v>
       </c>
-      <c r="I20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="J20" s="15">
+      <c r="I20" s="2">
+        <v>-999</v>
+      </c>
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M20" s="15">
-        <v>-999</v>
-      </c>
-      <c r="N20" s="16">
+      <c r="K20" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L20" s="2">
+        <v>-999</v>
+      </c>
+      <c r="M20" s="2">
+        <v>-999</v>
+      </c>
+      <c r="N20" s="2">
         <v>4</v>
       </c>
-      <c r="R20" s="14" t="s">
+      <c r="R20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S20" s="14" t="s">
+      <c r="S20" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="1">
         <v>16</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="G21" s="51">
-        <v>2</v>
-      </c>
-      <c r="R21" s="14" t="s">
+      <c r="G21" s="18">
+        <v>2</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S21" s="14" t="s">
+      <c r="S21" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="1">
         <v>17</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="G22" s="51">
-        <v>1</v>
-      </c>
-      <c r="R22" s="14" t="s">
+      <c r="G22" s="18">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S22" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="1">
         <v>18</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="G23" s="51">
-        <v>2</v>
-      </c>
-      <c r="R23" s="14" t="s">
+      <c r="G23" s="18">
+        <v>2</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="S23" s="14" t="s">
+      <c r="S23" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="1">
         <v>19</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="G24" s="51">
-        <v>-999</v>
-      </c>
-      <c r="R24" s="14" t="s">
+      <c r="G24" s="18">
+        <v>-999</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S24" s="14" t="s">
+      <c r="S24" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="1">
         <v>20</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="G25" s="42">
+      <c r="G25" s="18">
         <v>1.5</v>
       </c>
-      <c r="R25" s="14" t="s">
+      <c r="R25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S25" s="14" t="s">
+      <c r="S25" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="1">
         <v>21</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="18">
         <v>4</v>
       </c>
-      <c r="R26" s="14" t="s">
+      <c r="R26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="S26" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="1">
         <v>22</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="18">
         <v>4</v>
       </c>
-      <c r="R27" s="14" t="s">
+      <c r="R27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S27" s="14" t="s">
+      <c r="S27" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="1">
         <v>23</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="51">
+      <c r="G28" s="18">
         <v>4</v>
       </c>
-      <c r="R28" s="14" t="s">
+      <c r="R28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="S28" s="14" t="s">
+      <c r="S28" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="A29" s="1">
         <v>24</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="1">
         <v>22</v>
       </c>
-      <c r="G29" s="51">
-        <v>2</v>
-      </c>
-      <c r="R29" s="14" t="s">
+      <c r="G29" s="18">
+        <v>2</v>
+      </c>
+      <c r="R29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="S29" s="14" t="s">
+      <c r="S29" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="1">
         <v>25</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="1">
         <v>23</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="R30" s="14" t="s">
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="S30" s="14" t="s">
+      <c r="S30" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="A31" s="1">
         <v>26</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="1">
         <v>24</v>
       </c>
-      <c r="G31" s="51">
+      <c r="G31" s="18">
         <v>4.5</v>
       </c>
-      <c r="R31" s="14" t="s">
+      <c r="R31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S31" s="14" t="s">
+      <c r="S31" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="1">
         <v>27</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="1">
         <v>25</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="1">
         <v>5</v>
       </c>
-      <c r="R32" s="14" t="s">
+      <c r="R32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="S32" s="14" t="s">
+      <c r="S32" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="14">
+      <c r="A33" s="1">
         <v>28</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="1">
         <v>26</v>
       </c>
-      <c r="G33" s="51">
+      <c r="G33" s="18">
         <v>5</v>
       </c>
-      <c r="R33" s="14" t="s">
+      <c r="R33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="S33" s="14" t="s">
+      <c r="S33" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="1">
         <v>29</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="1">
         <v>27</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="1">
         <v>5</v>
       </c>
-      <c r="R34" s="14" t="s">
+      <c r="R34" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="S34" s="14" t="s">
+      <c r="S34" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="14">
+      <c r="A35" s="1">
         <v>30</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="1">
         <v>28</v>
       </c>
-      <c r="G35" s="51">
-        <v>3</v>
-      </c>
-      <c r="R35" s="14" t="s">
+      <c r="G35" s="18">
+        <v>3</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="S35" s="14" t="s">
+      <c r="S35" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="14">
+      <c r="A36" s="1">
         <v>31</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="1">
         <v>29</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="1">
         <v>5</v>
       </c>
-      <c r="R36" s="14" t="s">
+      <c r="R36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="S36" s="14" t="s">
+      <c r="S36" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
+      <c r="A37" s="1">
         <v>32</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="1">
         <v>30</v>
       </c>
-      <c r="G37" s="51">
+      <c r="G37" s="18">
         <v>5</v>
       </c>
-      <c r="R37" s="14" t="s">
+      <c r="R37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="S37" s="14" t="s">
+      <c r="S37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A38" s="14">
+      <c r="A38" s="1">
         <v>33</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="1">
         <v>31</v>
       </c>
-      <c r="G38" s="14">
-        <v>2</v>
-      </c>
-      <c r="R38" s="14" t="s">
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="S38" s="14" t="s">
+      <c r="S38" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A39" s="14">
+      <c r="A39" s="1">
         <v>34</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="1">
         <v>32</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="1">
         <v>4</v>
       </c>
-      <c r="R39" s="14" t="s">
+      <c r="R39" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S39" s="14" t="s">
+      <c r="S39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="14">
+      <c r="A40" s="1">
         <v>35</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="1">
         <v>33</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="1">
         <v>5</v>
       </c>
-      <c r="R40" s="14" t="s">
+      <c r="R40" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S40" s="14" t="s">
+      <c r="S40" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="14">
+      <c r="A41" s="1">
         <v>36</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="1">
         <v>34</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="1">
         <v>5</v>
       </c>
-      <c r="R41" s="14" t="s">
+      <c r="R41" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="S41" s="14" t="s">
+      <c r="S41" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" s="14">
+      <c r="A42" s="1">
         <v>37</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="1">
         <v>35</v>
       </c>
-      <c r="G42" s="14">
-        <v>2</v>
-      </c>
-      <c r="R42" s="14" t="s">
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S42" s="14" t="s">
+      <c r="S42" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="14">
+      <c r="A43" s="1">
         <v>38</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="1">
         <v>36</v>
       </c>
-      <c r="O43" s="17">
+      <c r="O43" s="4">
         <v>140</v>
       </c>
-      <c r="P43" s="17">
+      <c r="P43" s="4">
         <v>170</v>
       </c>
-      <c r="Q43" s="17" t="s">
+      <c r="Q43" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="R43" s="14" t="s">
+      <c r="R43" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="S43" s="14" t="s">
+      <c r="S43" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" s="14">
+      <c r="A44" s="1">
         <v>39</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="1">
         <v>37</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="4">
         <v>25</v>
       </c>
-      <c r="P44" s="17">
+      <c r="P44" s="4">
         <v>30</v>
       </c>
-      <c r="Q44" s="17" t="s">
+      <c r="Q44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="R44" s="14" t="s">
+      <c r="R44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="S44" s="14" t="s">
+      <c r="S44" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
+      <c r="A45" s="1">
         <v>40</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="1">
         <v>38</v>
       </c>
-      <c r="O45" s="17">
-        <v>1</v>
-      </c>
-      <c r="P45" s="17">
+      <c r="O45" s="4">
+        <v>1</v>
+      </c>
+      <c r="P45" s="4">
         <v>10</v>
       </c>
-      <c r="Q45" s="17" t="s">
+      <c r="Q45" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="R45" s="14" t="s">
+      <c r="R45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S45" s="14" t="s">
+      <c r="S45" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" s="14">
+      <c r="A46" s="1">
         <v>41</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="1">
         <v>39</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="4">
         <v>600</v>
       </c>
-      <c r="P46" s="17">
+      <c r="P46" s="4">
         <v>650</v>
       </c>
-      <c r="Q46" s="17" t="s">
+      <c r="Q46" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="R46" s="14" t="s">
+      <c r="R46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S46" s="14" t="s">
+      <c r="S46" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="14">
+      <c r="A47" s="1">
         <v>42</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="1">
         <v>40</v>
       </c>
       <c r="Q47" t="s">
         <v>174</v>
       </c>
-      <c r="R47" s="14" t="s">
+      <c r="R47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S47" s="14" t="s">
+      <c r="S47" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A48" s="14">
+      <c r="A48" s="1">
         <v>43</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="1">
         <v>41</v>
       </c>
       <c r="Q48" t="s">
         <v>174</v>
       </c>
-      <c r="R48" s="14" t="s">
+      <c r="R48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S48" s="14" t="s">
+      <c r="S48" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A49" s="14">
+      <c r="A49" s="1">
         <v>44</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="1">
         <v>42</v>
       </c>
-      <c r="O49" s="14">
+      <c r="O49" s="1">
         <v>0</v>
       </c>
-      <c r="P49" s="14">
+      <c r="P49" s="1">
         <v>0</v>
       </c>
-      <c r="Q49" s="14" t="s">
+      <c r="Q49" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="R49" s="14" t="s">
+      <c r="R49" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="S49" s="14" t="s">
+      <c r="S49" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A50" s="14">
+      <c r="A50" s="1">
         <v>45</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="1">
         <v>43</v>
       </c>
       <c r="Q50" t="s">
         <v>174</v>
       </c>
-      <c r="R50" s="14" t="s">
+      <c r="R50" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A51" s="14">
+      <c r="A51" s="1">
         <v>46</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="1">
         <v>44</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="1">
         <v>5</v>
       </c>
-      <c r="R51" s="14" t="s">
+      <c r="R51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="S51" s="14" t="s">
+      <c r="S51" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -8946,1412 +8914,1412 @@
   <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="14"/>
-    <col min="4" max="4" width="12.44140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="14"/>
-    <col min="6" max="6" width="21.88671875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="14" customWidth="1"/>
-    <col min="9" max="12" width="8.88671875" style="14"/>
-    <col min="13" max="13" width="14.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" style="14" customWidth="1"/>
-    <col min="15" max="16" width="8.88671875" style="14"/>
-    <col min="17" max="17" width="12.5546875" style="14" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="14"/>
+    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="12.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="21.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" style="1" customWidth="1"/>
+    <col min="9" max="12" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="14.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" style="1" customWidth="1"/>
+    <col min="15" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="12.5546875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32">
-        <v>2</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="33">
-        <v>2</v>
-      </c>
-      <c r="F3" s="33" t="s">
+    <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="11">
         <v>4.5</v>
       </c>
-      <c r="I3" s="34">
-        <v>2</v>
-      </c>
-      <c r="J3" s="34">
-        <v>-999</v>
-      </c>
-      <c r="K3" s="39">
-        <v>1</v>
-      </c>
-      <c r="L3" s="34">
+      <c r="I3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11">
+        <v>-999</v>
+      </c>
+      <c r="K3" s="40">
+        <v>-998</v>
+      </c>
+      <c r="L3" s="11">
         <v>4</v>
       </c>
-      <c r="M3" s="34">
-        <v>3</v>
-      </c>
-      <c r="N3" s="34">
-        <v>1</v>
-      </c>
-      <c r="R3" s="33" t="s">
+      <c r="M3" s="11">
+        <v>3</v>
+      </c>
+      <c r="N3" s="11">
+        <v>1</v>
+      </c>
+      <c r="R3" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="35">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="14">
-        <v>2</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I4" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36">
-        <v>2</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="37">
-        <v>2</v>
-      </c>
-      <c r="F5" s="37" t="s">
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="37">
-        <v>2</v>
-      </c>
-      <c r="S5" s="37" t="s">
+      <c r="I5" s="14">
+        <v>2</v>
+      </c>
+      <c r="S5" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32">
-        <v>3</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="33">
-        <v>3</v>
-      </c>
-      <c r="F6" s="33" t="s">
+    <row r="6" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H6" s="34">
-        <v>-999</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34">
-        <v>-999</v>
-      </c>
-      <c r="K6" s="39">
-        <v>2</v>
-      </c>
-      <c r="L6" s="34">
-        <v>3</v>
-      </c>
-      <c r="M6" s="34">
-        <v>1</v>
-      </c>
-      <c r="N6" s="34">
-        <v>1</v>
-      </c>
-      <c r="R6" s="33" t="s">
+      <c r="H6" s="11">
+        <v>-999</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11">
+        <v>-999</v>
+      </c>
+      <c r="K6" s="40">
+        <v>-998</v>
+      </c>
+      <c r="L6" s="11">
+        <v>3</v>
+      </c>
+      <c r="M6" s="11">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1</v>
+      </c>
+      <c r="R6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="S6" s="33" t="s">
+      <c r="S6" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="35">
-        <v>3</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="14">
-        <v>3</v>
-      </c>
-      <c r="F7" s="14" t="s">
+      <c r="A7" s="12">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36">
-        <v>3</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="37">
-        <v>3</v>
-      </c>
-      <c r="F8" s="37" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>3</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="14">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40">
-        <v>3</v>
-      </c>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16">
+        <v>3</v>
+      </c>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="B9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="15">
-        <v>-999</v>
-      </c>
-      <c r="I9" s="15">
-        <v>2</v>
-      </c>
-      <c r="J9" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K9" s="41">
-        <v>-999</v>
-      </c>
-      <c r="L9" s="18">
-        <v>1</v>
-      </c>
-      <c r="M9" s="41">
+      <c r="H9" s="2">
+        <v>-999</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K9" s="17">
+        <v>-999</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="17">
         <v>-998</v>
       </c>
-      <c r="N9" s="41">
+      <c r="N9" s="17">
         <v>-998</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="R9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="S9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32">
+    <row r="10" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="33">
+      <c r="B10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="10">
         <v>5</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="34">
-        <v>3</v>
-      </c>
-      <c r="I10" s="34">
-        <v>2</v>
-      </c>
-      <c r="J10" s="34">
-        <v>-999</v>
-      </c>
-      <c r="K10" s="34">
-        <v>-999</v>
-      </c>
-      <c r="L10" s="34">
-        <v>3</v>
-      </c>
-      <c r="M10" s="34">
-        <v>3</v>
-      </c>
-      <c r="N10" s="34">
+      <c r="H10" s="11">
+        <v>3</v>
+      </c>
+      <c r="I10" s="11">
+        <v>2</v>
+      </c>
+      <c r="J10" s="11">
+        <v>-999</v>
+      </c>
+      <c r="K10" s="11">
+        <v>-999</v>
+      </c>
+      <c r="L10" s="11">
+        <v>3</v>
+      </c>
+      <c r="M10" s="11">
+        <v>3</v>
+      </c>
+      <c r="N10" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="35">
+      <c r="A11" s="12">
         <v>5</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2">
         <v>1.5</v>
       </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="35">
+      <c r="A12" s="12">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="14">
+      <c r="B12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="1">
         <v>5</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2">
         <v>1.5</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-    </row>
-    <row r="13" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>5</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="37">
+      <c r="B13" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="14">
         <v>5</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="I13" s="37">
-        <v>1</v>
-      </c>
-      <c r="R13" s="37" t="s">
+      <c r="I13" s="14">
+        <v>1</v>
+      </c>
+      <c r="R13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="S13" s="37" t="s">
+      <c r="S13" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="1">
         <v>6</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="14">
+      <c r="B14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="1">
         <v>6</v>
       </c>
-      <c r="H14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="I14" s="15">
-        <v>3</v>
-      </c>
-      <c r="J14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="N14" s="15">
-        <v>-999</v>
-      </c>
-      <c r="R14" s="14" t="s">
+      <c r="H14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="I14" s="2">
+        <v>3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="M14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="N14" s="2">
+        <v>-999</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="1">
         <v>7</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="14">
+      <c r="B15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="1">
         <v>7</v>
       </c>
-      <c r="H15" s="15">
-        <v>-999</v>
-      </c>
-      <c r="I15" s="15">
-        <v>-999</v>
-      </c>
-      <c r="J15" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K15" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-999</v>
-      </c>
-      <c r="M15" s="15">
+      <c r="H15" s="2">
+        <v>-999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>-999</v>
+      </c>
+      <c r="J15" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K15" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L15" s="2">
+        <v>-999</v>
+      </c>
+      <c r="M15" s="2">
         <v>3.5</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="2">
         <v>3.5</v>
       </c>
-      <c r="R15" s="14" t="s">
+      <c r="R15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="S15" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
+      <c r="A16" s="1">
         <v>8</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="1">
         <v>8</v>
       </c>
-      <c r="G16" s="51">
-        <v>2</v>
-      </c>
-      <c r="R16" s="14" t="s">
+      <c r="G16" s="18">
+        <v>2</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="14">
+      <c r="B17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="1">
         <v>9</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G17" s="51"/>
-      <c r="I17" s="15">
+      <c r="G17" s="18"/>
+      <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K17" s="15">
+      <c r="J17" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="2">
         <v>0</v>
       </c>
-      <c r="M17" s="15">
-        <v>2</v>
-      </c>
-      <c r="N17" s="15">
-        <v>2</v>
-      </c>
-      <c r="R17" s="14" t="s">
+      <c r="M17" s="2">
+        <v>2</v>
+      </c>
+      <c r="N17" s="2">
+        <v>2</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B18" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="14">
+      <c r="B18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="1">
         <v>9</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G18" s="51"/>
-      <c r="H18" s="15">
+      <c r="G18" s="18"/>
+      <c r="H18" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="1">
         <v>10</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="1">
         <v>10</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="2">
         <v>0</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K19" s="15">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="15">
-        <v>1</v>
-      </c>
-      <c r="N19" s="15">
-        <v>2</v>
-      </c>
-      <c r="R19" s="14" t="s">
+      <c r="J19" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>2</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S19" s="14" t="s">
+      <c r="S19" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="1">
         <v>11</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="1">
         <v>11</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="2">
         <v>1000</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="2">
         <v>50000</v>
       </c>
-      <c r="Q20" s="15" t="s">
+      <c r="Q20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R20" s="14" t="s">
+      <c r="R20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S20" s="14" t="s">
+      <c r="S20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="1">
         <v>12</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="1">
         <v>12</v>
       </c>
-      <c r="O21" s="15">
+      <c r="O21" s="2">
         <v>50000</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="2">
         <v>100000</v>
       </c>
-      <c r="Q21" s="15" t="s">
+      <c r="Q21" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R21" s="14" t="s">
+      <c r="R21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S21" s="14" t="s">
+      <c r="S21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="1">
         <v>13</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="14">
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="1">
         <v>13</v>
       </c>
-      <c r="H22" s="15">
-        <v>2</v>
-      </c>
-      <c r="I22" s="15">
-        <v>1</v>
-      </c>
-      <c r="J22" s="15">
-        <v>-999</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L22" s="15">
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>-999</v>
+      </c>
+      <c r="K22" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L22" s="2">
         <v>0</v>
       </c>
-      <c r="M22" s="21">
-        <v>1</v>
-      </c>
-      <c r="N22" s="15">
-        <v>2</v>
-      </c>
-      <c r="R22" s="14" t="s">
+      <c r="M22" s="8">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
+        <v>2</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="1">
         <v>14</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="14">
+      <c r="B23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="1">
         <v>14</v>
       </c>
-      <c r="G23" s="51">
-        <v>2</v>
-      </c>
-      <c r="R23" s="14" t="s">
+      <c r="G23" s="18">
+        <v>2</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S23" s="14" t="s">
+      <c r="S23" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="1">
         <v>15</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="1">
         <v>15</v>
       </c>
-      <c r="H24" s="15">
-        <v>1</v>
-      </c>
-      <c r="I24" s="15">
-        <v>2</v>
-      </c>
-      <c r="J24" s="15">
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2">
         <v>4</v>
       </c>
-      <c r="K24" s="15">
-        <v>-999</v>
-      </c>
-      <c r="L24" s="15">
-        <v>1</v>
-      </c>
-      <c r="M24" s="15">
+      <c r="K24" s="2">
+        <v>-999</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
         <v>4</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="2">
         <v>4</v>
       </c>
-      <c r="R24" s="14" t="s">
+      <c r="R24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S24" s="14" t="s">
+      <c r="S24" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="32">
+    <row r="25" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
         <v>16</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="10">
         <v>16</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="52">
-        <v>1</v>
-      </c>
-      <c r="R25" s="33" t="s">
+      <c r="G25" s="19">
+        <v>1</v>
+      </c>
+      <c r="R25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36">
+    <row r="26" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
         <v>16</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="14">
         <v>16</v>
       </c>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="53">
+      <c r="G26" s="20">
         <v>0</v>
       </c>
-      <c r="R26" s="37" t="s">
+      <c r="R26" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="S26" s="37" t="s">
+      <c r="S26" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="1">
         <v>17</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="1">
         <v>17</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="18">
         <v>0</v>
       </c>
-      <c r="R27" s="14" t="s">
+      <c r="R27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S27" s="14" t="s">
+      <c r="S27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="1">
         <v>18</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="1">
         <v>18</v>
       </c>
-      <c r="G28" s="51">
-        <v>1</v>
-      </c>
-      <c r="R28" s="14" t="s">
+      <c r="G28" s="18">
+        <v>1</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="S28" s="14" t="s">
+      <c r="S28" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="A29" s="1">
         <v>19</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="1">
         <v>19</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="6">
         <v>999</v>
       </c>
-      <c r="R29" s="14" t="s">
+      <c r="R29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S29" s="14" t="s">
+      <c r="S29" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="1">
         <v>20</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="1">
         <v>20</v>
       </c>
-      <c r="G30" s="51">
-        <v>2</v>
-      </c>
-      <c r="R30" s="14" t="s">
+      <c r="G30" s="18">
+        <v>2</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S30" s="14" t="s">
+      <c r="S30" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="A31" s="1">
         <v>21</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="51">
-        <v>1</v>
-      </c>
-      <c r="R31" s="14" t="s">
+      <c r="G31" s="18">
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S31" s="14" t="s">
+      <c r="S31" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="1">
         <v>22</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G32" s="51">
+      <c r="G32" s="18">
         <v>4</v>
       </c>
-      <c r="R32" s="14" t="s">
+      <c r="R32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S32" s="14" t="s">
+      <c r="S32" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="14">
+      <c r="A33" s="1">
         <v>23</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G33" s="51">
-        <v>1</v>
-      </c>
-      <c r="R33" s="14" t="s">
+      <c r="G33" s="18">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="S33" s="14" t="s">
+      <c r="S33" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="1">
         <v>24</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="1">
         <v>22</v>
       </c>
-      <c r="G34" s="51">
-        <v>1</v>
-      </c>
-      <c r="R34" s="14" t="s">
+      <c r="G34" s="18">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="S34" s="14" t="s">
+      <c r="S34" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="14">
+      <c r="A35" s="1">
         <v>25</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="1">
         <v>23</v>
       </c>
-      <c r="G35" s="14">
-        <v>3</v>
-      </c>
-      <c r="R35" s="14" t="s">
+      <c r="G35" s="1">
+        <v>3</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="S35" s="14" t="s">
+      <c r="S35" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="14">
+      <c r="A36" s="1">
         <v>26</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="1">
         <v>24</v>
       </c>
-      <c r="G36" s="51">
+      <c r="G36" s="18">
         <v>4</v>
       </c>
-      <c r="R36" s="14" t="s">
+      <c r="R36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S36" s="14" t="s">
+      <c r="S36" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
+      <c r="A37" s="1">
         <v>27</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="1">
         <v>25</v>
       </c>
-      <c r="G37" s="38">
-        <v>2</v>
-      </c>
-      <c r="R37" s="14" t="s">
+      <c r="G37" s="15">
+        <v>2</v>
+      </c>
+      <c r="R37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="S37" s="14" t="s">
+      <c r="S37" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A38" s="14">
+      <c r="A38" s="1">
         <v>28</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="1">
         <v>26</v>
       </c>
-      <c r="G38" s="51">
+      <c r="G38" s="18">
         <v>4</v>
       </c>
-      <c r="R38" s="14" t="s">
+      <c r="R38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="S38" s="14" t="s">
+      <c r="S38" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A39" s="14">
+      <c r="A39" s="1">
         <v>29</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="1">
         <v>27</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="1">
         <v>5</v>
       </c>
-      <c r="R39" s="14" t="s">
+      <c r="R39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="S39" s="14" t="s">
+      <c r="S39" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="14">
+      <c r="A40" s="1">
         <v>30</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="1">
         <v>28</v>
       </c>
-      <c r="G40" s="51">
+      <c r="G40" s="18">
         <v>5</v>
       </c>
-      <c r="R40" s="14" t="s">
+      <c r="R40" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="S40" s="14" t="s">
+      <c r="S40" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="14">
+      <c r="A41" s="1">
         <v>31</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="1">
         <v>29</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="1">
         <v>4</v>
       </c>
-      <c r="R41" s="14" t="s">
+      <c r="R41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="S41" s="14" t="s">
+      <c r="S41" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" s="14">
+      <c r="A42" s="1">
         <v>32</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="1">
         <v>30</v>
       </c>
-      <c r="G42" s="51">
+      <c r="G42" s="18">
         <v>5</v>
       </c>
-      <c r="R42" s="14" t="s">
+      <c r="R42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="S42" s="14" t="s">
+      <c r="S42" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="14">
+      <c r="A43" s="1">
         <v>33</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="1">
         <v>31</v>
       </c>
-      <c r="G43" s="20">
-        <v>3</v>
-      </c>
-      <c r="R43" s="14" t="s">
+      <c r="G43" s="7">
+        <v>3</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="S43" s="14" t="s">
+      <c r="S43" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" s="14">
+      <c r="A44" s="1">
         <v>34</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="1">
         <v>32</v>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="7">
         <v>5</v>
       </c>
-      <c r="R44" s="14" t="s">
+      <c r="R44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="S44" s="14" t="s">
+      <c r="S44" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
+      <c r="A45" s="1">
         <v>35</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="1">
         <v>33</v>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="7">
         <v>4.5</v>
       </c>
-      <c r="R45" s="14" t="s">
+      <c r="R45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S45" s="14" t="s">
+      <c r="S45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A46" s="14">
+      <c r="A46" s="1">
         <v>36</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="1">
         <v>34</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="7">
         <v>4</v>
       </c>
-      <c r="R46" s="14" t="s">
+      <c r="R46" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="S46" s="14" t="s">
+      <c r="S46" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A47" s="14">
+      <c r="A47" s="1">
         <v>37</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="1">
         <v>35</v>
       </c>
-      <c r="G47" s="20">
-        <v>2</v>
-      </c>
-      <c r="R47" s="14" t="s">
+      <c r="G47" s="7">
+        <v>2</v>
+      </c>
+      <c r="R47" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S47" s="14" t="s">
+      <c r="S47" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:19" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="32">
+    <row r="48" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9">
         <v>38</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="10">
         <v>36</v>
       </c>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54" t="s">
+      <c r="O48" s="21"/>
+      <c r="P48" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="Q48" s="54" t="s">
+      <c r="Q48" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="R48" s="33" t="s">
+      <c r="R48" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="S48" s="33" t="s">
+      <c r="S48" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A49" s="35">
+      <c r="A49" s="12">
         <v>39</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="1">
         <v>37</v>
       </c>
-      <c r="O49" s="17" t="s">
+      <c r="O49" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="P49" s="17" t="s">
+      <c r="P49" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="Q49" s="17" t="s">
+      <c r="Q49" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="R49" s="14" t="s">
+      <c r="R49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="S49" s="14" t="s">
+      <c r="S49" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A50" s="35">
+      <c r="A50" s="12">
         <v>40</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="1">
         <v>38</v>
       </c>
-      <c r="O50" s="17" t="s">
+      <c r="O50" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P50" s="17" t="s">
+      <c r="P50" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="Q50" s="17" t="s">
+      <c r="Q50" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="R50" s="14" t="s">
+      <c r="R50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S50" s="14" t="s">
+      <c r="S50" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A51" s="35">
+      <c r="A51" s="12">
         <v>41</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="1">
         <v>39</v>
       </c>
-      <c r="O51" s="17">
+      <c r="O51" s="4">
         <v>5</v>
       </c>
-      <c r="P51" s="17" t="s">
+      <c r="P51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q51" s="17" t="s">
+      <c r="Q51" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="R51" s="14" t="s">
+      <c r="R51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S51" s="14" t="s">
+      <c r="S51" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A52" s="35">
+      <c r="A52" s="12">
         <v>42</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="1">
         <v>40</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O52" s="4">
         <v>50</v>
       </c>
-      <c r="P52" s="17">
+      <c r="P52" s="4">
         <v>100</v>
       </c>
-      <c r="Q52" s="17" t="s">
+      <c r="Q52" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="R52" s="14" t="s">
+      <c r="R52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S52" s="14" t="s">
+      <c r="S52" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A53" s="35">
+      <c r="A53" s="12">
         <v>43</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="1">
         <v>41</v>
       </c>
-      <c r="O53" s="17">
+      <c r="O53" s="4">
         <v>60000</v>
       </c>
-      <c r="P53" s="17" t="s">
+      <c r="P53" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="Q53" s="17" t="s">
+      <c r="Q53" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="R53" s="14" t="s">
+      <c r="R53" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S53" s="14" t="s">
+      <c r="S53" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A54" s="35">
+      <c r="A54" s="12">
         <v>44</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="1">
         <v>42</v>
       </c>
-      <c r="O54" s="17">
+      <c r="O54" s="4">
         <v>20</v>
       </c>
-      <c r="Q54" s="17" t="s">
+      <c r="Q54" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="R54" s="14" t="s">
+      <c r="R54" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="S54" s="14" t="s">
+      <c r="S54" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A55" s="35">
+      <c r="A55" s="12">
         <v>45</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="1">
         <v>43</v>
       </c>
       <c r="Q55" t="s">
         <v>174</v>
       </c>
-      <c r="R55" s="14" t="s">
+      <c r="R55" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="36">
+    <row r="56" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
         <v>46</v>
       </c>
-      <c r="B56" s="37" t="s">
+      <c r="B56" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="37">
+      <c r="C56" s="14">
         <v>44</v>
       </c>
-      <c r="G56" s="37">
+      <c r="G56" s="14">
         <v>5</v>
       </c>
       <c r="Q56"/>
-      <c r="R56" s="37" t="s">
+      <c r="R56" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S56" s="37" t="s">
+      <c r="S56" s="14" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/questionnaires_coded.xlsx
+++ b/data/questionnaires_coded.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC06370-BAE3-4DD2-B796-D95C9D0ECD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEDE4D4-A582-4C74-9796-A81225EC9924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="I_1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="182">
   <si>
     <t>If the [extreme event] happen, how likely are you to go out fishing?</t>
   </si>
@@ -114,9 +114,6 @@
     <t>long_description</t>
   </si>
   <si>
-    <t>go_out</t>
-  </si>
-  <si>
     <t>catchability</t>
   </si>
   <si>
@@ -286,9 +283,6 @@
   </si>
   <si>
     <t>identity</t>
-  </si>
-  <si>
-    <t>home</t>
   </si>
   <si>
     <t>unc_31_34</t>
@@ -592,6 +586,21 @@
   </si>
   <si>
     <t>whitefish</t>
+  </si>
+  <si>
+    <t>unc_46</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>go_fishing</t>
+  </si>
+  <si>
+    <t>sense_of_home</t>
+  </si>
+  <si>
+    <t>substitution_capacity</t>
   </si>
 </sst>
 </file>
@@ -731,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -835,10 +844,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1122,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
@@ -1140,46 +1145,46 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -1188,7 +1193,7 @@
         <v>23</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" t="s">
         <v>25</v>
@@ -1202,19 +1207,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2" t="s">
         <v>102</v>
-      </c>
-      <c r="R2" t="s">
-        <v>103</v>
-      </c>
-      <c r="S2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1222,13 +1227,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="23">
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I3" s="24">
         <v>4</v>
@@ -1254,19 +1259,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="27">
         <v>2</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="25">
         <v>1</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="S4" s="27" t="s">
         <v>0</v>
@@ -1277,13 +1282,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="23">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H5" s="24">
         <v>5</v>
@@ -1297,13 +1302,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="23">
         <v>3</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H6" s="28"/>
       <c r="I6" s="24">
@@ -1330,13 +1335,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="27">
         <v>3</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" s="25">
         <v>1</v>
@@ -1348,13 +1353,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="23">
         <v>3</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H8" s="24">
         <v>5</v>
@@ -1362,7 +1367,7 @@
       <c r="J8" s="24"/>
       <c r="M8" s="24"/>
       <c r="R8" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S8" s="23" t="s">
         <v>19</v>
@@ -1373,7 +1378,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1394,13 +1399,13 @@
         <v>-998</v>
       </c>
       <c r="M9" s="30">
-        <v>-997</v>
+        <v>2</v>
       </c>
       <c r="N9" s="28">
         <v>-998</v>
       </c>
       <c r="R9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S9" t="s">
         <v>20</v>
@@ -1411,7 +1416,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1438,7 +1443,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S10" t="s">
         <v>21</v>
@@ -1449,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1476,7 +1481,7 @@
         <v>-999</v>
       </c>
       <c r="R11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S11" t="s">
         <v>1</v>
@@ -1487,7 +1492,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1514,10 +1519,10 @@
         <v>-999</v>
       </c>
       <c r="R12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" t="s">
         <v>32</v>
-      </c>
-      <c r="S12" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -1525,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -1534,10 +1539,10 @@
         <v>1.5</v>
       </c>
       <c r="R13" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" t="s">
         <v>34</v>
-      </c>
-      <c r="S13" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -1545,13 +1550,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H14" s="28"/>
       <c r="I14" s="28">
@@ -1573,10 +1578,10 @@
         <v>2</v>
       </c>
       <c r="R14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -1584,13 +1589,13 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>9</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H15" s="28">
         <v>1</v>
@@ -1601,7 +1606,7 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -1628,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="R16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S16" t="s">
         <v>24</v>
@@ -1639,7 +1644,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C17">
         <v>11</v>
@@ -1651,13 +1656,13 @@
         <v>20000</v>
       </c>
       <c r="Q17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -1665,7 +1670,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>12</v>
@@ -1677,13 +1682,13 @@
         <v>6000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" t="s">
         <v>40</v>
-      </c>
-      <c r="S18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -1691,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>13</v>
@@ -1718,10 +1723,10 @@
         <v>-999</v>
       </c>
       <c r="R19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -1729,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20">
         <v>14</v>
@@ -1738,10 +1743,10 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -1749,7 +1754,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21">
         <v>15</v>
@@ -1776,10 +1781,10 @@
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -1787,7 +1792,7 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>16</v>
@@ -1799,7 +1804,7 @@
         <v>12</v>
       </c>
       <c r="S22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -1807,7 +1812,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23">
         <v>17</v>
@@ -1819,7 +1824,7 @@
         <v>11</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -1827,7 +1832,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24">
         <v>18</v>
@@ -1836,10 +1841,10 @@
         <v>2</v>
       </c>
       <c r="R24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -1847,7 +1852,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25">
         <v>19</v>
@@ -1856,10 +1861,10 @@
         <v>2</v>
       </c>
       <c r="R25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -1867,7 +1872,7 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26">
         <v>20</v>
@@ -1876,10 +1881,10 @@
         <v>2</v>
       </c>
       <c r="R26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S26" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -1887,19 +1892,19 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="R27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S27" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -1907,19 +1912,19 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="R28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S28" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -1927,19 +1932,19 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29">
         <v>4</v>
       </c>
       <c r="R29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S29" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -1947,7 +1952,7 @@
         <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C30">
         <v>22</v>
@@ -1956,10 +1961,10 @@
         <v>4</v>
       </c>
       <c r="R30" t="s">
+        <v>67</v>
+      </c>
+      <c r="S30" t="s">
         <v>68</v>
-      </c>
-      <c r="S30" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -1967,7 +1972,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31">
         <v>23</v>
@@ -1976,7 +1981,7 @@
         <v>3</v>
       </c>
       <c r="R31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S31" t="s">
         <v>10</v>
@@ -1987,7 +1992,7 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C32">
         <v>24</v>
@@ -1996,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="R32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S32" t="s">
         <v>9</v>
@@ -2007,7 +2012,7 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C33">
         <v>25</v>
@@ -2016,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S33" t="s">
         <v>8</v>
@@ -2027,7 +2032,7 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C34">
         <v>26</v>
@@ -2036,10 +2041,10 @@
         <v>2</v>
       </c>
       <c r="R34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -2047,7 +2052,7 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35">
         <v>27</v>
@@ -2056,7 +2061,7 @@
         <v>5</v>
       </c>
       <c r="R35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S35" t="s">
         <v>7</v>
@@ -2067,7 +2072,7 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C36">
         <v>28</v>
@@ -2076,10 +2081,10 @@
         <v>3</v>
       </c>
       <c r="R36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -2087,7 +2092,7 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37">
         <v>29</v>
@@ -2096,10 +2101,10 @@
         <v>5</v>
       </c>
       <c r="R37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
@@ -2107,7 +2112,7 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C38">
         <v>30</v>
@@ -2116,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s">
         <v>6</v>
@@ -2127,7 +2132,7 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39">
         <v>31</v>
@@ -2136,10 +2141,10 @@
         <v>5</v>
       </c>
       <c r="R39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
@@ -2147,7 +2152,7 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40">
         <v>32</v>
@@ -2156,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="R40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S40" t="s">
         <v>5</v>
@@ -2167,7 +2172,7 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C41">
         <v>33</v>
@@ -2176,7 +2181,7 @@
         <v>5</v>
       </c>
       <c r="R41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S41" t="s">
         <v>4</v>
@@ -2187,7 +2192,7 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C42">
         <v>34</v>
@@ -2196,7 +2201,7 @@
         <v>5</v>
       </c>
       <c r="R42" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="S42" t="s">
         <v>3</v>
@@ -2207,7 +2212,7 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43">
         <v>35</v>
@@ -2216,10 +2221,10 @@
         <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -2227,7 +2232,7 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C44">
         <v>36</v>
@@ -2236,7 +2241,7 @@
         <v>100</v>
       </c>
       <c r="R44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S44" t="s">
         <v>13</v>
@@ -2247,7 +2252,7 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45">
         <v>37</v>
@@ -2259,10 +2264,10 @@
         <v>8000</v>
       </c>
       <c r="Q45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S45" t="s">
         <v>14</v>
@@ -2273,7 +2278,7 @@
         <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46">
         <v>38</v>
@@ -2285,13 +2290,13 @@
         <v>10000</v>
       </c>
       <c r="Q46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R46" t="s">
         <v>15</v>
       </c>
       <c r="S46" s="29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
@@ -2299,7 +2304,7 @@
         <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C47">
         <v>39</v>
@@ -2311,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="Q47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R47" t="s">
         <v>16</v>
       </c>
       <c r="S47" s="29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -2325,7 +2330,7 @@
         <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48">
         <v>40</v>
@@ -2337,13 +2342,13 @@
         <v>500</v>
       </c>
       <c r="Q48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R48" t="s">
         <v>17</v>
       </c>
       <c r="S48" s="29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -2351,7 +2356,7 @@
         <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49">
         <v>41</v>
@@ -2363,13 +2368,13 @@
         <v>3000</v>
       </c>
       <c r="Q49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R49" t="s">
         <v>18</v>
       </c>
       <c r="S49" s="29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -2377,19 +2382,19 @@
         <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50">
         <v>42</v>
       </c>
       <c r="Q50" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R50" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S50" s="29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -2397,16 +2402,16 @@
         <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C51">
         <v>43</v>
       </c>
       <c r="Q51" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
@@ -2414,7 +2419,7 @@
         <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52">
         <v>44</v>
@@ -2423,10 +2428,10 @@
         <v>5</v>
       </c>
       <c r="R52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S52" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
@@ -2434,7 +2439,7 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C53">
         <v>45</v>
@@ -2443,7 +2448,41 @@
         <v>-999</v>
       </c>
       <c r="R53" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
+        <v>48</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="R54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="12">
+        <v>49</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" s="1">
+        <v>47</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2455,7 +2494,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FABCB46-76B1-45AE-9EC3-251841A9849E}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -2476,46 +2515,46 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -2524,7 +2563,7 @@
         <v>23</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" t="s">
         <v>25</v>
@@ -2538,19 +2577,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2558,7 +2597,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2584,8 +2623,8 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
-        <v>27</v>
+      <c r="R3" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S3" t="s">
         <v>0</v>
@@ -2596,7 +2635,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2623,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S4" t="s">
         <v>19</v>
@@ -2634,7 +2673,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -2661,7 +2700,7 @@
         <v>-998</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S5" t="s">
         <v>20</v>
@@ -2672,13 +2711,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -2704,13 +2743,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I7" s="28">
         <v>1</v>
@@ -2726,19 +2765,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="R8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S8" t="s">
         <v>21</v>
@@ -2749,7 +2788,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -2776,7 +2815,7 @@
         <v>-999</v>
       </c>
       <c r="R9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S9" t="s">
         <v>1</v>
@@ -2787,7 +2826,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -2814,10 +2853,10 @@
         <v>3</v>
       </c>
       <c r="R10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" t="s">
         <v>32</v>
-      </c>
-      <c r="S10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -2825,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -2834,10 +2873,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" t="s">
         <v>34</v>
-      </c>
-      <c r="S11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -2845,7 +2884,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -2872,10 +2911,10 @@
         <v>2</v>
       </c>
       <c r="R12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2883,22 +2922,22 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13">
         <v>10</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="28">
         <v>0</v>
       </c>
       <c r="I13" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="28">
         <v>1</v>
       </c>
       <c r="K13" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="28">
         <v>1</v>
@@ -2910,7 +2949,7 @@
         <v>1.5</v>
       </c>
       <c r="R13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S13" t="s">
         <v>24</v>
@@ -2921,7 +2960,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14">
         <v>11</v>
@@ -2933,13 +2972,13 @@
         <v>50000</v>
       </c>
       <c r="Q14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -2947,7 +2986,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>12</v>
@@ -2959,13 +2998,13 @@
         <v>500000</v>
       </c>
       <c r="Q15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R15" t="s">
+        <v>39</v>
+      </c>
+      <c r="S15" t="s">
         <v>40</v>
-      </c>
-      <c r="S15" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -2973,7 +3012,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -3000,10 +3039,10 @@
         <v>2</v>
       </c>
       <c r="R16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -3011,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>14</v>
@@ -3020,10 +3059,10 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -3031,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -3058,10 +3097,10 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -3069,7 +3108,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>16</v>
@@ -3081,7 +3120,7 @@
         <v>12</v>
       </c>
       <c r="S19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -3089,7 +3128,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20">
         <v>17</v>
@@ -3101,7 +3140,7 @@
         <v>11</v>
       </c>
       <c r="S20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -3109,7 +3148,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21">
         <v>18</v>
@@ -3118,10 +3157,10 @@
         <v>999</v>
       </c>
       <c r="R21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -3129,7 +3168,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>19</v>
@@ -3138,10 +3177,10 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -3149,7 +3188,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23">
         <v>20</v>
@@ -3158,10 +3197,10 @@
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -3169,19 +3208,19 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="R24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -3189,19 +3228,19 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="R25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -3209,19 +3248,19 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="R26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -3229,7 +3268,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -3238,10 +3277,10 @@
         <v>5</v>
       </c>
       <c r="R27" t="s">
+        <v>67</v>
+      </c>
+      <c r="S27" t="s">
         <v>68</v>
-      </c>
-      <c r="S27" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -3249,7 +3288,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>23</v>
@@ -3258,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S28" t="s">
         <v>10</v>
@@ -3269,7 +3308,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>24</v>
@@ -3278,7 +3317,7 @@
         <v>5</v>
       </c>
       <c r="R29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S29" t="s">
         <v>9</v>
@@ -3289,7 +3328,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>25</v>
@@ -3298,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S30" t="s">
         <v>8</v>
@@ -3309,7 +3348,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -3318,10 +3357,10 @@
         <v>5</v>
       </c>
       <c r="R31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -3329,7 +3368,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32">
         <v>27</v>
@@ -3338,7 +3377,7 @@
         <v>5</v>
       </c>
       <c r="R32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S32" t="s">
         <v>7</v>
@@ -3349,7 +3388,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C33">
         <v>28</v>
@@ -3358,10 +3397,10 @@
         <v>5</v>
       </c>
       <c r="R33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -3369,7 +3408,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34">
         <v>29</v>
@@ -3378,10 +3417,10 @@
         <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -3389,7 +3428,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35">
         <v>30</v>
@@ -3398,7 +3437,7 @@
         <v>5</v>
       </c>
       <c r="R35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s">
         <v>6</v>
@@ -3409,7 +3448,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -3418,10 +3457,10 @@
         <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -3429,7 +3468,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C37">
         <v>32</v>
@@ -3438,7 +3477,7 @@
         <v>4</v>
       </c>
       <c r="R37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s">
         <v>5</v>
@@ -3449,7 +3488,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>33</v>
@@ -3458,7 +3497,7 @@
         <v>4</v>
       </c>
       <c r="R38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S38" t="s">
         <v>4</v>
@@ -3469,7 +3508,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>34</v>
@@ -3478,7 +3517,7 @@
         <v>4</v>
       </c>
       <c r="R39" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="S39" t="s">
         <v>3</v>
@@ -3489,7 +3528,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40">
         <v>35</v>
@@ -3498,10 +3537,10 @@
         <v>2</v>
       </c>
       <c r="R40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -3509,7 +3548,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C41">
         <v>36</v>
@@ -3521,10 +3560,10 @@
         <v>100</v>
       </c>
       <c r="Q41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S41" t="s">
         <v>13</v>
@@ -3535,7 +3574,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C42">
         <v>37</v>
@@ -3547,10 +3586,10 @@
         <v>1500000</v>
       </c>
       <c r="Q42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S42" t="s">
         <v>14</v>
@@ -3561,7 +3600,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>38</v>
@@ -3573,13 +3612,13 @@
         <v>500000</v>
       </c>
       <c r="Q43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R43" t="s">
         <v>15</v>
       </c>
       <c r="S43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -3587,19 +3626,19 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <v>39</v>
       </c>
       <c r="Q44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R44" t="s">
         <v>16</v>
       </c>
       <c r="S44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -3607,19 +3646,19 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45">
         <v>40</v>
       </c>
       <c r="Q45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R45" t="s">
         <v>17</v>
       </c>
       <c r="S45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
@@ -3627,19 +3666,19 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46">
         <v>41</v>
       </c>
       <c r="Q46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R46" t="s">
         <v>18</v>
       </c>
       <c r="S46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
@@ -3647,7 +3686,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C47">
         <v>42</v>
@@ -3659,13 +3698,13 @@
         <v>3</v>
       </c>
       <c r="Q47" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S47" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -3673,16 +3712,16 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48">
         <v>43</v>
       </c>
       <c r="Q48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -3690,7 +3729,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49">
         <v>44</v>
@@ -3699,10 +3738,10 @@
         <v>5</v>
       </c>
       <c r="R49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -3710,7 +3749,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C50">
         <v>45</v>
@@ -3719,7 +3758,41 @@
         <v>-999</v>
       </c>
       <c r="R50" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="R51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="12">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -3730,51 +3803,51 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B51270F-FFBC-4EA1-B493-B161BDCA8EC1}">
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -3783,7 +3856,7 @@
         <v>23</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" t="s">
         <v>25</v>
@@ -3797,19 +3870,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3817,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -3843,8 +3916,8 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
-        <v>27</v>
+      <c r="R3" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S3" t="s">
         <v>0</v>
@@ -3855,13 +3928,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="27">
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H4" s="27">
         <v>-999</v>
@@ -3884,13 +3957,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -3901,13 +3974,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -3924,13 +3997,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="23">
         <v>3</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M7" s="35">
         <v>4</v>
@@ -3939,7 +4012,7 @@
         <v>4</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>19</v>
@@ -3950,7 +4023,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -3977,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S8" t="s">
         <v>20</v>
@@ -3988,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -4015,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S9" t="s">
         <v>21</v>
@@ -4026,7 +4099,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -4053,7 +4126,7 @@
         <v>-999</v>
       </c>
       <c r="R10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S10" t="s">
         <v>1</v>
@@ -4064,7 +4137,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -4091,10 +4164,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" t="s">
         <v>32</v>
-      </c>
-      <c r="S11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -4102,7 +4175,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -4111,10 +4184,10 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" t="s">
         <v>34</v>
-      </c>
-      <c r="S12" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -4122,7 +4195,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -4149,10 +4222,10 @@
         <v>-998</v>
       </c>
       <c r="R13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -4160,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -4168,7 +4241,7 @@
       <c r="H14">
         <v>-999</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
@@ -4187,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="R14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S14" t="s">
         <v>24</v>
@@ -4198,7 +4271,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -4210,13 +4283,13 @@
         <v>50000</v>
       </c>
       <c r="Q15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4224,7 +4297,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -4236,13 +4309,13 @@
         <v>200000</v>
       </c>
       <c r="Q16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" t="s">
         <v>40</v>
-      </c>
-      <c r="S16" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -4250,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -4277,10 +4350,10 @@
         <v>-998</v>
       </c>
       <c r="R17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -4288,7 +4361,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -4297,10 +4370,10 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -4308,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -4335,10 +4408,10 @@
         <v>2</v>
       </c>
       <c r="R19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -4346,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -4358,7 +4431,7 @@
         <v>12</v>
       </c>
       <c r="S20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4366,7 +4439,7 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21">
         <v>17</v>
@@ -4378,7 +4451,7 @@
         <v>11</v>
       </c>
       <c r="S21" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4386,7 +4459,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>18</v>
@@ -4395,10 +4468,10 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S22" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4406,7 +4479,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23">
         <v>19</v>
@@ -4415,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S23" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4426,7 +4499,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -4435,10 +4508,10 @@
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S24" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4446,19 +4519,19 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S25" s="34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4466,19 +4539,19 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="R26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S26" s="34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4486,19 +4559,19 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27">
         <v>3</v>
       </c>
       <c r="R27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S27" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -4506,7 +4579,7 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C28">
         <v>22</v>
@@ -4515,10 +4588,10 @@
         <v>1</v>
       </c>
       <c r="R28" t="s">
+        <v>67</v>
+      </c>
+      <c r="S28" t="s">
         <v>68</v>
-      </c>
-      <c r="S28" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -4526,7 +4599,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>23</v>
@@ -4535,7 +4608,7 @@
         <v>5</v>
       </c>
       <c r="R29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S29" t="s">
         <v>10</v>
@@ -4546,7 +4619,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>24</v>
@@ -4555,7 +4628,7 @@
         <v>5</v>
       </c>
       <c r="R30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S30" t="s">
         <v>9</v>
@@ -4566,7 +4639,7 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31">
         <v>25</v>
@@ -4575,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S31" t="s">
         <v>8</v>
@@ -4586,7 +4659,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C32">
         <v>26</v>
@@ -4595,10 +4668,10 @@
         <v>5</v>
       </c>
       <c r="R32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -4606,7 +4679,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C33">
         <v>27</v>
@@ -4615,7 +4688,7 @@
         <v>5</v>
       </c>
       <c r="R33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S33" t="s">
         <v>7</v>
@@ -4626,7 +4699,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34">
         <v>28</v>
@@ -4635,10 +4708,10 @@
         <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -4646,7 +4719,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35">
         <v>29</v>
@@ -4655,10 +4728,10 @@
         <v>5</v>
       </c>
       <c r="R35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -4666,7 +4739,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -4675,7 +4748,7 @@
         <v>5</v>
       </c>
       <c r="R36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S36" t="s">
         <v>6</v>
@@ -4686,7 +4759,7 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37">
         <v>31</v>
@@ -4695,10 +4768,10 @@
         <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
@@ -4706,7 +4779,7 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>32</v>
@@ -4715,7 +4788,7 @@
         <v>5</v>
       </c>
       <c r="R38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s">
         <v>5</v>
@@ -4726,7 +4799,7 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>33</v>
@@ -4735,7 +4808,7 @@
         <v>5</v>
       </c>
       <c r="R39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s">
         <v>4</v>
@@ -4746,7 +4819,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40">
         <v>34</v>
@@ -4755,7 +4828,7 @@
         <v>5</v>
       </c>
       <c r="R40" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="S40" t="s">
         <v>3</v>
@@ -4766,7 +4839,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C41">
         <v>35</v>
@@ -4775,10 +4848,10 @@
         <v>2</v>
       </c>
       <c r="R41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -4786,7 +4859,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <v>36</v>
@@ -4798,10 +4871,10 @@
         <v>150</v>
       </c>
       <c r="Q42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S42" t="s">
         <v>13</v>
@@ -4812,7 +4885,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>37</v>
@@ -4824,10 +4897,10 @@
         <v>15000</v>
       </c>
       <c r="Q43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R43" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S43" t="s">
         <v>14</v>
@@ -4838,7 +4911,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <v>38</v>
@@ -4850,13 +4923,13 @@
         <v>200000</v>
       </c>
       <c r="Q44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R44" t="s">
         <v>15</v>
       </c>
       <c r="S44" s="34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4864,7 +4937,7 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45">
         <v>39</v>
@@ -4876,13 +4949,13 @@
         <v>2500</v>
       </c>
       <c r="Q45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R45" t="s">
         <v>16</v>
       </c>
       <c r="S45" s="34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4890,7 +4963,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46">
         <v>40</v>
@@ -4902,13 +4975,13 @@
         <v>5000</v>
       </c>
       <c r="Q46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R46" t="s">
         <v>17</v>
       </c>
       <c r="S46" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4916,7 +4989,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C47">
         <v>41</v>
@@ -4928,13 +5001,13 @@
         <v>200</v>
       </c>
       <c r="Q47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R47" t="s">
         <v>18</v>
       </c>
       <c r="S47" s="34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4942,7 +5015,7 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48">
         <v>42</v>
@@ -4954,13 +5027,13 @@
         <v>30</v>
       </c>
       <c r="Q48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R48" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S48" s="34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -4968,16 +5041,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49">
         <v>43</v>
       </c>
       <c r="Q49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -4985,7 +5058,7 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50">
         <v>44</v>
@@ -4994,10 +5067,10 @@
         <v>2</v>
       </c>
       <c r="R50" s="34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S50" s="34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -5005,7 +5078,7 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C51">
         <v>45</v>
@@ -5014,7 +5087,41 @@
         <v>-999</v>
       </c>
       <c r="R51" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="12">
+        <v>48</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="R52" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
+        <v>49</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" s="1">
+        <v>47</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -5024,7 +5131,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD628265-A169-414F-BB6E-7496B95E445F}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="17" max="17" width="12.5546875" customWidth="1"/>
@@ -5032,46 +5139,46 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -5080,7 +5187,7 @@
         <v>23</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" t="s">
         <v>25</v>
@@ -5094,19 +5201,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5114,7 +5221,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -5140,8 +5247,8 @@
       <c r="N3" s="28">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
-        <v>27</v>
+      <c r="R3" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S3" t="s">
         <v>0</v>
@@ -5152,18 +5259,18 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="27">
         <v>3</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25">
         <v>2</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="41">
         <v>3</v>
       </c>
       <c r="J4" s="25">
@@ -5182,7 +5289,7 @@
         <v>2</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S4" s="27" t="s">
         <v>19</v>
@@ -5193,13 +5300,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="23">
         <v>3</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I5" s="23">
         <v>4</v>
@@ -5210,7 +5317,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5237,7 +5344,7 @@
         <v>-998</v>
       </c>
       <c r="R6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S6" t="s">
         <v>20</v>
@@ -5248,7 +5355,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5275,7 +5382,7 @@
         <v>-998</v>
       </c>
       <c r="R7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S7" t="s">
         <v>21</v>
@@ -5286,7 +5393,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -5313,7 +5420,7 @@
         <v>-999</v>
       </c>
       <c r="R8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" t="s">
         <v>1</v>
@@ -5324,7 +5431,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -5351,10 +5458,10 @@
         <v>5</v>
       </c>
       <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" t="s">
         <v>32</v>
-      </c>
-      <c r="S9" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -5362,7 +5469,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -5371,10 +5478,10 @@
         <v>2</v>
       </c>
       <c r="R10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" t="s">
         <v>34</v>
-      </c>
-      <c r="S10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -5382,7 +5489,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -5409,10 +5516,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -5420,7 +5527,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -5447,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S12" t="s">
         <v>24</v>
@@ -5458,7 +5565,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -5470,13 +5577,13 @@
         <v>2500</v>
       </c>
       <c r="Q13" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -5484,7 +5591,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -5496,13 +5603,13 @@
         <v>5000</v>
       </c>
       <c r="Q14" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" t="s">
         <v>40</v>
-      </c>
-      <c r="S14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -5510,7 +5617,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -5537,10 +5644,10 @@
         <v>2</v>
       </c>
       <c r="R15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -5548,7 +5655,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -5557,10 +5664,10 @@
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -5568,7 +5675,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -5595,10 +5702,10 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -5606,7 +5713,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -5618,7 +5725,7 @@
         <v>12</v>
       </c>
       <c r="S18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -5626,7 +5733,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -5638,7 +5745,7 @@
         <v>11</v>
       </c>
       <c r="S19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -5646,7 +5753,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20">
         <v>18</v>
@@ -5655,10 +5762,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -5666,7 +5773,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21">
         <v>19</v>
@@ -5675,10 +5782,10 @@
         <v>999</v>
       </c>
       <c r="R21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -5686,7 +5793,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -5695,10 +5802,10 @@
         <v>2</v>
       </c>
       <c r="R22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -5706,19 +5813,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G23" s="28">
         <v>3</v>
       </c>
       <c r="R23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -5726,19 +5833,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G24" s="28">
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -5746,19 +5853,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="28">
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -5766,7 +5873,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26">
         <v>22</v>
@@ -5775,10 +5882,10 @@
         <v>2</v>
       </c>
       <c r="R26" t="s">
+        <v>67</v>
+      </c>
+      <c r="S26" t="s">
         <v>68</v>
-      </c>
-      <c r="S26" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -5786,7 +5893,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C27">
         <v>23</v>
@@ -5795,7 +5902,7 @@
         <v>-999</v>
       </c>
       <c r="R27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S27" t="s">
         <v>10</v>
@@ -5806,7 +5913,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>24</v>
@@ -5815,7 +5922,7 @@
         <v>2</v>
       </c>
       <c r="R28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S28" t="s">
         <v>9</v>
@@ -5826,7 +5933,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -5835,7 +5942,7 @@
         <v>-999</v>
       </c>
       <c r="R29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S29" t="s">
         <v>8</v>
@@ -5846,7 +5953,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -5855,10 +5962,10 @@
         <v>2</v>
       </c>
       <c r="R30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -5866,7 +5973,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C31">
         <v>27</v>
@@ -5875,7 +5982,7 @@
         <v>5</v>
       </c>
       <c r="R31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S31" t="s">
         <v>7</v>
@@ -5886,7 +5993,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32">
         <v>28</v>
@@ -5895,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -5906,7 +6013,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C33">
         <v>29</v>
@@ -5915,10 +6022,10 @@
         <v>3</v>
       </c>
       <c r="R33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -5926,7 +6033,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34">
         <v>30</v>
@@ -5935,7 +6042,7 @@
         <v>5</v>
       </c>
       <c r="R34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S34" t="s">
         <v>6</v>
@@ -5946,7 +6053,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -5955,10 +6062,10 @@
         <v>2</v>
       </c>
       <c r="R35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -5966,7 +6073,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -5975,7 +6082,7 @@
         <v>5</v>
       </c>
       <c r="R36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s">
         <v>5</v>
@@ -5986,7 +6093,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C37">
         <v>33</v>
@@ -5995,7 +6102,7 @@
         <v>3</v>
       </c>
       <c r="R37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s">
         <v>4</v>
@@ -6006,7 +6113,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>34</v>
@@ -6015,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="R38" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="S38" t="s">
         <v>3</v>
@@ -6026,7 +6133,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>35</v>
@@ -6035,10 +6142,10 @@
         <v>2</v>
       </c>
       <c r="R39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
@@ -6046,7 +6153,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40">
         <v>36</v>
@@ -6056,10 +6163,10 @@
       </c>
       <c r="P40" s="28"/>
       <c r="Q40" s="28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S40" t="s">
         <v>13</v>
@@ -6070,17 +6177,17 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C41">
         <v>37</v>
       </c>
       <c r="O41" s="36"/>
       <c r="Q41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S41" t="s">
         <v>14</v>
@@ -6091,7 +6198,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C42">
         <v>38</v>
@@ -6101,13 +6208,13 @@
         <v>5000</v>
       </c>
       <c r="Q42" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R42" t="s">
         <v>15</v>
       </c>
       <c r="S42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -6115,7 +6222,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>39</v>
@@ -6127,13 +6234,13 @@
         <v>20000</v>
       </c>
       <c r="Q43" s="28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R43" t="s">
         <v>16</v>
       </c>
       <c r="S43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -6141,19 +6248,19 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <v>40</v>
       </c>
       <c r="Q44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R44" t="s">
         <v>17</v>
       </c>
       <c r="S44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
@@ -6161,19 +6268,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45">
         <v>41</v>
       </c>
       <c r="Q45" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R45" t="s">
         <v>18</v>
       </c>
       <c r="S45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
@@ -6181,19 +6288,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46">
         <v>42</v>
       </c>
       <c r="Q46" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R46" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
@@ -6201,16 +6308,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C47">
         <v>43</v>
       </c>
       <c r="Q47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R47" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -6218,7 +6325,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48">
         <v>44</v>
@@ -6227,10 +6334,10 @@
         <v>5</v>
       </c>
       <c r="R48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S48" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -6238,7 +6345,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C49">
         <v>45</v>
@@ -6247,7 +6354,41 @@
         <v>-999</v>
       </c>
       <c r="R49" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="12">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46</v>
+      </c>
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+      <c r="R50" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="1">
+        <v>47</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6257,51 +6398,51 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26691114-F8EB-4EEB-B292-06EA58F9BDCC}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -6310,7 +6451,7 @@
         <v>23</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" t="s">
         <v>25</v>
@@ -6321,16 +6462,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -6338,35 +6479,35 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="27">
         <v>2</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I3" s="37"/>
       <c r="J3" s="37">
         <v>1</v>
       </c>
       <c r="K3" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="L3" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>134</v>
-      </c>
       <c r="R3" s="27" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -6374,13 +6515,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I4">
         <v>5</v>
@@ -6391,13 +6532,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -6408,13 +6549,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -6425,13 +6566,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -6442,13 +6583,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="23">
         <v>2</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I8" s="23">
         <v>2</v>
@@ -6459,13 +6600,13 @@
         <v>3</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="27">
         <v>3</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H9" s="37">
         <v>-997</v>
@@ -6481,13 +6622,13 @@
         <v>3</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N9" s="37">
         <v>-998</v>
       </c>
       <c r="R9" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -6495,13 +6636,13 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="32">
@@ -6518,13 +6659,13 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32">
@@ -6541,13 +6682,13 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="32">
@@ -6564,13 +6705,13 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="32">
@@ -6587,13 +6728,13 @@
         <v>3</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="23">
         <v>3</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H14" s="38"/>
       <c r="I14" s="38">
@@ -6610,7 +6751,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -6637,7 +6778,7 @@
         <v>999</v>
       </c>
       <c r="R15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -6645,7 +6786,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -6672,7 +6813,7 @@
         <v>3</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -6680,7 +6821,7 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -6707,7 +6848,7 @@
         <v>-999</v>
       </c>
       <c r="R17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -6715,7 +6856,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>7</v>
@@ -6742,7 +6883,7 @@
         <v>-999</v>
       </c>
       <c r="R18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -6750,7 +6891,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -6759,7 +6900,7 @@
         <v>5</v>
       </c>
       <c r="R19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -6767,7 +6908,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20">
         <v>9</v>
@@ -6794,7 +6935,7 @@
         <v>2</v>
       </c>
       <c r="R20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -6802,7 +6943,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -6829,7 +6970,7 @@
         <v>3</v>
       </c>
       <c r="R21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -6837,7 +6978,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22">
         <v>11</v>
@@ -6849,10 +6990,10 @@
         <v>50000</v>
       </c>
       <c r="Q22" s="32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -6860,7 +7001,7 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23">
         <v>12</v>
@@ -6872,10 +7013,10 @@
         <v>1000000</v>
       </c>
       <c r="Q23" s="32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.3">
@@ -6883,13 +7024,13 @@
         <v>13</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" s="27">
         <v>13</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H24" s="37">
         <v>2</v>
@@ -6911,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="R24" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -6919,13 +7060,13 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C25">
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -6939,13 +7080,13 @@
         <v>13</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C26" s="23">
         <v>13</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I26" s="23">
         <v>2</v>
@@ -6956,7 +7097,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27">
         <v>14</v>
@@ -6965,7 +7106,7 @@
         <v>5</v>
       </c>
       <c r="R27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -6973,7 +7114,7 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28">
         <v>15</v>
@@ -7000,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -7008,7 +7149,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29">
         <v>16</v>
@@ -7025,7 +7166,7 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C30">
         <v>17</v>
@@ -7042,7 +7183,7 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C31">
         <v>18</v>
@@ -7051,7 +7192,7 @@
         <v>2</v>
       </c>
       <c r="R31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -7059,7 +7200,7 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C32">
         <v>19</v>
@@ -7068,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -7076,7 +7217,7 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C33">
         <v>20</v>
@@ -7085,7 +7226,7 @@
         <v>4</v>
       </c>
       <c r="R33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -7093,16 +7234,16 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G34" s="28">
         <v>1</v>
       </c>
       <c r="R34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -7110,16 +7251,16 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G35" s="28">
         <v>1</v>
       </c>
       <c r="R35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -7127,16 +7268,16 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="28">
         <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -7144,7 +7285,7 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C37">
         <v>22</v>
@@ -7153,7 +7294,7 @@
         <v>2</v>
       </c>
       <c r="R37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -7161,7 +7302,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C38">
         <v>23</v>
@@ -7170,7 +7311,7 @@
         <v>-999</v>
       </c>
       <c r="R38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -7178,7 +7319,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C39">
         <v>24</v>
@@ -7187,7 +7328,7 @@
         <v>4</v>
       </c>
       <c r="R39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -7195,7 +7336,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C40">
         <v>25</v>
@@ -7204,7 +7345,7 @@
         <v>-999</v>
       </c>
       <c r="R40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -7212,7 +7353,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41">
         <v>26</v>
@@ -7221,7 +7362,7 @@
         <v>4</v>
       </c>
       <c r="R41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -7229,7 +7370,7 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42">
         <v>27</v>
@@ -7238,7 +7379,7 @@
         <v>4</v>
       </c>
       <c r="R42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -7246,7 +7387,7 @@
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C43">
         <v>28</v>
@@ -7255,7 +7396,7 @@
         <v>5</v>
       </c>
       <c r="R43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
@@ -7263,16 +7404,16 @@
         <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C44">
         <v>29</v>
       </c>
       <c r="G44">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="R44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
@@ -7280,7 +7421,7 @@
         <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45">
         <v>30</v>
@@ -7289,7 +7430,7 @@
         <v>3</v>
       </c>
       <c r="R45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -7297,7 +7438,7 @@
         <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46">
         <v>31</v>
@@ -7306,7 +7447,7 @@
         <v>4</v>
       </c>
       <c r="R46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
@@ -7314,7 +7455,7 @@
         <v>34</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C47">
         <v>32</v>
@@ -7323,7 +7464,7 @@
         <v>4</v>
       </c>
       <c r="R47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
@@ -7331,7 +7472,7 @@
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C48">
         <v>33</v>
@@ -7340,7 +7481,7 @@
         <v>3</v>
       </c>
       <c r="R48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -7348,7 +7489,7 @@
         <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49">
         <v>34</v>
@@ -7357,7 +7498,7 @@
         <v>4</v>
       </c>
       <c r="R49" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -7365,7 +7506,7 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C50">
         <v>35</v>
@@ -7374,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="R50" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
@@ -7382,22 +7523,22 @@
         <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C51">
         <v>36</v>
       </c>
       <c r="O51" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="P51" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q51" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="P51" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q51" s="36" t="s">
-        <v>138</v>
-      </c>
       <c r="R51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
@@ -7405,17 +7546,17 @@
         <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52">
         <v>37</v>
       </c>
       <c r="O52" s="36"/>
       <c r="Q52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
@@ -7423,19 +7564,19 @@
         <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C53">
         <v>38</v>
       </c>
       <c r="O53" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="P53" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="P53" s="36" t="s">
-        <v>139</v>
-      </c>
       <c r="Q53" s="36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R53" t="s">
         <v>15</v>
@@ -7446,7 +7587,7 @@
         <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C54">
         <v>39</v>
@@ -7455,10 +7596,10 @@
         <v>30</v>
       </c>
       <c r="P54" s="36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q54" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R54" t="s">
         <v>16</v>
@@ -7469,7 +7610,7 @@
         <v>42</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -7478,10 +7619,10 @@
         <v>20</v>
       </c>
       <c r="P55" s="36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q55" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R55" t="s">
         <v>17</v>
@@ -7492,13 +7633,13 @@
         <v>43</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C56">
         <v>41</v>
       </c>
       <c r="Q56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R56" t="s">
         <v>18</v>
@@ -7509,7 +7650,7 @@
         <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C57">
         <v>42</v>
@@ -7518,13 +7659,13 @@
         <v>999</v>
       </c>
       <c r="P57" s="36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q57" s="36" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R57" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
@@ -7532,16 +7673,16 @@
         <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58">
         <v>43</v>
       </c>
       <c r="Q58" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R58" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
@@ -7549,7 +7690,7 @@
         <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59">
         <v>44</v>
@@ -7558,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="R59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
@@ -7566,7 +7707,7 @@
         <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C60">
         <v>45</v>
@@ -7575,7 +7716,41 @@
         <v>-999</v>
       </c>
       <c r="R60" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="12">
+        <v>48</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46</v>
+      </c>
+      <c r="G61" s="1">
+        <v>3</v>
+      </c>
+      <c r="R61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="12">
+        <v>49</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="1">
+        <v>47</v>
+      </c>
+      <c r="G62" s="1">
+        <v>5</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -7585,56 +7760,57 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2FA0D2-7332-491F-A427-CDB5433B2771}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="8.88671875" style="1"/>
     <col min="17" max="17" width="12.5546875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="1"/>
+    <col min="18" max="18" width="13" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>22</v>
@@ -7643,7 +7819,7 @@
         <v>23</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>25</v>
@@ -7657,19 +7833,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -7677,35 +7853,35 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="10">
         <v>2</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I3" s="11">
         <v>1.5</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L3" s="11">
         <v>5</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>27</v>
+        <v>132</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>0</v>
@@ -7716,19 +7892,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M4" s="1">
         <v>4</v>
       </c>
-      <c r="R4" s="14" t="s">
-        <v>27</v>
+      <c r="R4" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>0</v>
@@ -7739,19 +7915,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="14">
         <v>2</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M5" s="14">
         <v>1</v>
       </c>
-      <c r="R5" s="14" t="s">
-        <v>27</v>
+      <c r="R5" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>0</v>
@@ -7762,20 +7938,21 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>169</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F6" s="1"/>
       <c r="H6" s="11">
         <v>3</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K6" s="11">
         <v>1</v>
@@ -7790,7 +7967,7 @@
         <v>2</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S6" s="10" t="s">
         <v>19</v>
@@ -7801,13 +7978,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I7" s="1">
         <v>2</v>
@@ -7818,14 +7995,15 @@
         <v>3</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="14">
         <v>3</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>171</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="I8" s="14">
         <v>4</v>
       </c>
@@ -7835,7 +8013,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -7862,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>20</v>
@@ -7873,13 +8051,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -7900,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>21</v>
@@ -7911,7 +8089,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -7938,7 +8116,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>1</v>
@@ -7949,7 +8127,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -7958,7 +8136,7 @@
         <v>4</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J12" s="2">
         <v>-999</v>
@@ -7976,10 +8154,10 @@
         <v>-999</v>
       </c>
       <c r="R12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -7987,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -7997,10 +8175,10 @@
       </c>
       <c r="H13" s="4"/>
       <c r="R13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -8008,7 +8186,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
@@ -8032,13 +8210,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -8046,7 +8224,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -8073,7 +8251,7 @@
         <v>3</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>24</v>
@@ -8084,7 +8262,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
@@ -8096,13 +8274,13 @@
         <v>50000</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -8110,7 +8288,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
@@ -8122,13 +8300,13 @@
         <v>500000</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -8136,7 +8314,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1">
         <v>13</v>
@@ -8163,10 +8341,10 @@
         <v>2</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -8174,7 +8352,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C19" s="1">
         <v>14</v>
@@ -8183,10 +8361,10 @@
         <v>4</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -8194,7 +8372,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1">
         <v>15</v>
@@ -8221,10 +8399,10 @@
         <v>4</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -8232,7 +8410,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1">
         <v>16</v>
@@ -8244,7 +8422,7 @@
         <v>12</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -8252,7 +8430,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1">
         <v>17</v>
@@ -8264,7 +8442,7 @@
         <v>11</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -8272,7 +8450,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" s="1">
         <v>18</v>
@@ -8281,10 +8459,10 @@
         <v>2</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -8292,7 +8470,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1">
         <v>19</v>
@@ -8301,10 +8479,10 @@
         <v>-999</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -8312,7 +8490,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" s="1">
         <v>20</v>
@@ -8321,10 +8499,10 @@
         <v>1.5</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -8332,19 +8510,19 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G26" s="18">
         <v>4</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -8352,19 +8530,19 @@
         <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G27" s="18">
         <v>4</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -8372,19 +8550,19 @@
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="18">
         <v>4</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -8392,7 +8570,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C29" s="1">
         <v>22</v>
@@ -8401,10 +8579,10 @@
         <v>2</v>
       </c>
       <c r="R29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -8412,7 +8590,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30" s="1">
         <v>23</v>
@@ -8421,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>10</v>
@@ -8432,7 +8610,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="1">
         <v>24</v>
@@ -8441,7 +8619,7 @@
         <v>4.5</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>9</v>
@@ -8452,7 +8630,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C32" s="1">
         <v>25</v>
@@ -8461,7 +8639,7 @@
         <v>5</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>8</v>
@@ -8472,7 +8650,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -8481,10 +8659,10 @@
         <v>5</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -8492,7 +8670,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34" s="1">
         <v>27</v>
@@ -8501,7 +8679,7 @@
         <v>5</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>7</v>
@@ -8512,7 +8690,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35" s="1">
         <v>28</v>
@@ -8521,10 +8699,10 @@
         <v>3</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -8532,7 +8710,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C36" s="1">
         <v>29</v>
@@ -8541,10 +8719,10 @@
         <v>5</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -8552,7 +8730,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37" s="1">
         <v>30</v>
@@ -8561,7 +8739,7 @@
         <v>5</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>6</v>
@@ -8572,7 +8750,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C38" s="1">
         <v>31</v>
@@ -8581,10 +8759,10 @@
         <v>2</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
@@ -8592,7 +8770,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C39" s="1">
         <v>32</v>
@@ -8601,7 +8779,7 @@
         <v>4</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>5</v>
@@ -8612,7 +8790,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40" s="1">
         <v>33</v>
@@ -8621,7 +8799,7 @@
         <v>5</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>4</v>
@@ -8632,7 +8810,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C41" s="1">
         <v>34</v>
@@ -8640,8 +8818,8 @@
       <c r="G41" s="1">
         <v>5</v>
       </c>
-      <c r="R41" s="1" t="s">
-        <v>85</v>
+      <c r="R41" t="s">
+        <v>180</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>3</v>
@@ -8652,7 +8830,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C42" s="1">
         <v>35</v>
@@ -8661,10 +8839,10 @@
         <v>2</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -8672,7 +8850,7 @@
         <v>38</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C43" s="1">
         <v>36</v>
@@ -8684,10 +8862,10 @@
         <v>170</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>13</v>
@@ -8698,7 +8876,7 @@
         <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1">
         <v>37</v>
@@ -8710,10 +8888,10 @@
         <v>30</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>14</v>
@@ -8724,7 +8902,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C45" s="1">
         <v>38</v>
@@ -8736,13 +8914,13 @@
         <v>10</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>15</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
@@ -8750,7 +8928,7 @@
         <v>41</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1">
         <v>39</v>
@@ -8762,13 +8940,13 @@
         <v>650</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>16</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
@@ -8776,19 +8954,19 @@
         <v>42</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C47" s="1">
         <v>40</v>
       </c>
       <c r="Q47" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
@@ -8796,19 +8974,19 @@
         <v>43</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1">
         <v>41</v>
       </c>
       <c r="Q48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>18</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
@@ -8816,7 +8994,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49" s="1">
         <v>42</v>
@@ -8828,13 +9006,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
@@ -8842,16 +9020,16 @@
         <v>45</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1">
         <v>43</v>
       </c>
       <c r="Q50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -8859,7 +9037,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C51" s="1">
         <v>44</v>
@@ -8868,10 +9046,10 @@
         <v>5</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
@@ -8879,7 +9057,7 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C52">
         <v>45</v>
@@ -8901,7 +9079,41 @@
       <c r="P52"/>
       <c r="Q52"/>
       <c r="R52" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
+        <v>48</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="R53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
+        <v>49</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="1">
+        <v>47</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -8911,7 +9123,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40DC07B-E25F-4A7F-9959-D54B043EB346}">
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="1"/>
@@ -8930,46 +9142,46 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>22</v>
@@ -8978,7 +9190,7 @@
         <v>23</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>25</v>
@@ -8992,19 +9204,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -9012,13 +9224,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="10">
         <v>2</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H3" s="11">
         <v>4.5</v>
@@ -9041,8 +9253,8 @@
       <c r="N3" s="11">
         <v>1</v>
       </c>
-      <c r="R3" s="10" t="s">
-        <v>27</v>
+      <c r="R3" s="27" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -9050,13 +9262,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
@@ -9067,13 +9279,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="14">
         <v>2</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I5" s="14">
         <v>2</v>
@@ -9087,13 +9299,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H6" s="11">
         <v>-999</v>
@@ -9115,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S6" s="10" t="s">
         <v>19</v>
@@ -9126,13 +9338,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2">
@@ -9149,13 +9361,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="14">
         <v>3</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16">
@@ -9172,7 +9384,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -9199,7 +9411,7 @@
         <v>-998</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>20</v>
@@ -9210,13 +9422,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10" s="10">
         <v>5</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H10" s="11">
         <v>3</v>
@@ -9245,13 +9457,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2">
@@ -9268,13 +9480,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2">
@@ -9291,19 +9503,19 @@
         <v>5</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="14">
         <v>5</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I13" s="14">
         <v>1</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>21</v>
@@ -9314,7 +9526,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1">
         <v>6</v>
@@ -9341,7 +9553,7 @@
         <v>-999</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>1</v>
@@ -9352,7 +9564,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1">
         <v>7</v>
@@ -9379,10 +9591,10 @@
         <v>3.5</v>
       </c>
       <c r="R15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -9390,7 +9602,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="1">
         <v>8</v>
@@ -9399,21 +9611,21 @@
         <v>2</v>
       </c>
       <c r="R16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="1">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G17" s="18"/>
       <c r="I17" s="2">
@@ -9435,21 +9647,21 @@
         <v>2</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1">
         <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="2">
@@ -9461,7 +9673,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C19" s="1">
         <v>10</v>
@@ -9488,7 +9700,7 @@
         <v>2</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>24</v>
@@ -9499,7 +9711,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C20" s="1">
         <v>11</v>
@@ -9511,13 +9723,13 @@
         <v>50000</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -9525,7 +9737,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1">
         <v>12</v>
@@ -9537,13 +9749,13 @@
         <v>100000</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S21" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -9551,7 +9763,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C22" s="1">
         <v>13</v>
@@ -9578,10 +9790,10 @@
         <v>2</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -9589,7 +9801,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1">
         <v>14</v>
@@ -9598,10 +9810,10 @@
         <v>2</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -9609,7 +9821,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1">
         <v>15</v>
@@ -9636,10 +9848,10 @@
         <v>4</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -9647,13 +9859,13 @@
         <v>16</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" s="10">
         <v>16</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G25" s="19">
         <v>1</v>
@@ -9662,7 +9874,7 @@
         <v>12</v>
       </c>
       <c r="S25" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -9670,13 +9882,13 @@
         <v>16</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26" s="14">
         <v>16</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G26" s="20">
         <v>0</v>
@@ -9685,7 +9897,7 @@
         <v>12</v>
       </c>
       <c r="S26" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -9693,7 +9905,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C27" s="1">
         <v>17</v>
@@ -9705,7 +9917,7 @@
         <v>11</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -9713,7 +9925,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1">
         <v>18</v>
@@ -9722,10 +9934,10 @@
         <v>1</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -9733,7 +9945,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="1">
         <v>19</v>
@@ -9742,10 +9954,10 @@
         <v>999</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -9753,7 +9965,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C30" s="1">
         <v>20</v>
@@ -9762,10 +9974,10 @@
         <v>2</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -9773,19 +9985,19 @@
         <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G31" s="18">
         <v>1</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -9793,19 +10005,19 @@
         <v>22</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G32" s="18">
         <v>4</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -9813,19 +10025,19 @@
         <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" s="18">
         <v>1</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -9833,7 +10045,7 @@
         <v>24</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1">
         <v>22</v>
@@ -9842,10 +10054,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -9853,7 +10065,7 @@
         <v>25</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1">
         <v>23</v>
@@ -9862,7 +10074,7 @@
         <v>3</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>10</v>
@@ -9873,7 +10085,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C36" s="1">
         <v>24</v>
@@ -9882,7 +10094,7 @@
         <v>4</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>9</v>
@@ -9893,7 +10105,7 @@
         <v>27</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1">
         <v>25</v>
@@ -9902,7 +10114,7 @@
         <v>2</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>8</v>
@@ -9913,7 +10125,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1">
         <v>26</v>
@@ -9922,10 +10134,10 @@
         <v>4</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
@@ -9933,7 +10145,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" s="1">
         <v>27</v>
@@ -9942,7 +10154,7 @@
         <v>5</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>7</v>
@@ -9953,7 +10165,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1">
         <v>28</v>
@@ -9962,10 +10174,10 @@
         <v>5</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -9973,7 +10185,7 @@
         <v>31</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C41" s="1">
         <v>29</v>
@@ -9982,10 +10194,10 @@
         <v>4</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -9993,7 +10205,7 @@
         <v>32</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="1">
         <v>30</v>
@@ -10002,7 +10214,7 @@
         <v>5</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>6</v>
@@ -10013,7 +10225,7 @@
         <v>33</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C43" s="1">
         <v>31</v>
@@ -10022,10 +10234,10 @@
         <v>3</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
@@ -10033,7 +10245,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C44" s="1">
         <v>32</v>
@@ -10042,7 +10254,7 @@
         <v>5</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>5</v>
@@ -10053,7 +10265,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C45" s="1">
         <v>33</v>
@@ -10062,7 +10274,7 @@
         <v>4.5</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>4</v>
@@ -10073,7 +10285,7 @@
         <v>36</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C46" s="1">
         <v>34</v>
@@ -10081,8 +10293,8 @@
       <c r="G46" s="7">
         <v>4</v>
       </c>
-      <c r="R46" s="1" t="s">
-        <v>85</v>
+      <c r="R46" t="s">
+        <v>180</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>3</v>
@@ -10093,7 +10305,7 @@
         <v>37</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1">
         <v>35</v>
@@ -10102,10 +10314,10 @@
         <v>2</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -10113,20 +10325,20 @@
         <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C48" s="10">
         <v>36</v>
       </c>
       <c r="O48" s="21"/>
       <c r="P48" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q48" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S48" s="10" t="s">
         <v>13</v>
@@ -10137,22 +10349,22 @@
         <v>39</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49" s="1">
         <v>37</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q49" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="P49" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q49" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="R49" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>14</v>
@@ -10163,25 +10375,25 @@
         <v>40</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C50" s="1">
         <v>38</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>15</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
@@ -10189,7 +10401,7 @@
         <v>41</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C51" s="1">
         <v>39</v>
@@ -10198,16 +10410,16 @@
         <v>5</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>16</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
@@ -10215,7 +10427,7 @@
         <v>42</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52" s="1">
         <v>40</v>
@@ -10227,13 +10439,13 @@
         <v>100</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
@@ -10241,7 +10453,7 @@
         <v>43</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C53" s="1">
         <v>41</v>
@@ -10250,16 +10462,16 @@
         <v>60000</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>18</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
@@ -10267,7 +10479,7 @@
         <v>44</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C54" s="1">
         <v>42</v>
@@ -10276,13 +10488,13 @@
         <v>20</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
@@ -10290,16 +10502,16 @@
         <v>45</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C55" s="1">
         <v>43</v>
       </c>
       <c r="Q55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -10307,7 +10519,7 @@
         <v>46</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C56" s="14">
         <v>44</v>
@@ -10317,10 +10529,10 @@
       </c>
       <c r="Q56"/>
       <c r="R56" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S56" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
@@ -10328,7 +10540,7 @@
         <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C57">
         <v>45</v>
@@ -10348,9 +10560,42 @@
       <c r="N57"/>
       <c r="O57"/>
       <c r="P57"/>
-      <c r="Q57"/>
       <c r="R57" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="12">
+        <v>48</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46</v>
+      </c>
+      <c r="G58" s="1">
+        <v>3</v>
+      </c>
+      <c r="R58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" s="12">
+        <v>49</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="1">
+        <v>47</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
